--- a/AAII_Financials/Quarterly/WEBC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WEBC_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>WEBC</t>
   </si>
@@ -656,403 +656,442 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45138</v>
+      </c>
+      <c r="G7" s="2">
         <v>45046</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>44957</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
         <v>44865</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>44773</v>
       </c>
-      <c r="H7" s="2">
+      <c r="K7" s="2">
         <v>44681</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>44592</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>44500</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>44408</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>44316</v>
       </c>
-      <c r="M7" s="2">
+      <c r="P7" s="2">
         <v>44227</v>
       </c>
-      <c r="N7" s="2">
+      <c r="Q7" s="2">
         <v>44135</v>
       </c>
-      <c r="O7" s="2">
+      <c r="R7" s="2">
         <v>44043</v>
       </c>
-      <c r="P7" s="2">
+      <c r="S7" s="2">
         <v>43951</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="T7" s="2">
         <v>43861</v>
       </c>
-      <c r="R7" s="2">
+      <c r="U7" s="2">
         <v>43769</v>
       </c>
-      <c r="S7" s="2">
+      <c r="V7" s="2">
         <v>43677</v>
       </c>
-      <c r="T7" s="2">
+      <c r="W7" s="2">
         <v>43585</v>
       </c>
-      <c r="U7" s="2">
+      <c r="X7" s="2">
         <v>43496</v>
       </c>
-      <c r="V7" s="2">
+      <c r="Y7" s="2">
         <v>43404</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Z7" s="2">
         <v>43312</v>
       </c>
-      <c r="X7" s="2">
+      <c r="AA7" s="2">
         <v>43220</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AB7" s="2">
         <v>43131</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AC7" s="2">
         <v>43039</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AD7" s="2">
         <v>42947</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AE7" s="2">
         <v>42855</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AF7" s="2">
         <v>42766</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AG7" s="2">
         <v>42674</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AH7" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>146000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>157800</v>
+      </c>
+      <c r="F8" s="3">
+        <v>156400</v>
+      </c>
+      <c r="G8" s="3">
         <v>168600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="H8" s="3">
         <v>173400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="I8" s="3">
         <v>188500</v>
       </c>
-      <c r="G8" s="3">
-        <v>704000</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
+        <v>172500</v>
+      </c>
+      <c r="K8" s="3">
         <v>190600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="L8" s="3">
         <v>173400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="M8" s="3">
         <v>167500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="N8" s="3">
         <v>145500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="O8" s="3">
         <v>127000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="P8" s="3">
         <v>94300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="Q8" s="3">
         <v>99800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="R8" s="3">
         <v>89100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="S8" s="3">
         <v>104800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="T8" s="3">
         <v>112400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="U8" s="3">
         <v>122500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="V8" s="3">
         <v>130000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="W8" s="3">
         <v>145700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="X8" s="3">
         <v>135900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="Y8" s="3">
         <v>137000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Z8" s="3">
         <v>147800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="AA8" s="3">
         <v>127300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AB8" s="3">
         <v>111000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AC8" s="3">
         <v>114300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AD8" s="3">
         <v>106600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AE8" s="3">
         <v>98300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AF8" s="3">
         <v>91600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AG8" s="3">
         <v>88300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AH8" s="3">
         <v>84000</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>133000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>136200</v>
+      </c>
+      <c r="F9" s="3">
+        <v>131900</v>
+      </c>
+      <c r="G9" s="3">
         <v>145000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="H9" s="3">
         <v>158100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="I9" s="3">
         <v>162500</v>
       </c>
-      <c r="G9" s="3">
-        <v>585900</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
+        <v>151400</v>
+      </c>
+      <c r="K9" s="3">
         <v>157100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="L9" s="3">
         <v>144300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="M9" s="3">
         <v>133100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="N9" s="3">
         <v>116900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="O9" s="3">
         <v>108400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="P9" s="3">
         <v>87000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="Q9" s="3">
         <v>92500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="R9" s="3">
         <v>86300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="S9" s="3">
         <v>94900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="T9" s="3">
         <v>100700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="U9" s="3">
         <v>108900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="V9" s="3">
         <v>118600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="W9" s="3">
         <v>126000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="X9" s="3">
         <v>117500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="Y9" s="3">
         <v>112800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Z9" s="3">
         <v>123700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="AA9" s="3">
         <v>108700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AB9" s="3">
         <v>98000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AC9" s="3">
         <v>100400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AD9" s="3">
         <v>96400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AE9" s="3">
         <v>89400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AF9" s="3">
         <v>84000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AG9" s="3">
         <v>80400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AH9" s="3">
         <v>77300</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>21600</v>
+      </c>
+      <c r="F10" s="3">
+        <v>24500</v>
+      </c>
+      <c r="G10" s="3">
         <v>23600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="H10" s="3">
         <v>15300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="I10" s="3">
         <v>26000</v>
       </c>
-      <c r="G10" s="3">
-        <v>118100</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
+        <v>21100</v>
+      </c>
+      <c r="K10" s="3">
         <v>33500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="L10" s="3">
         <v>29100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="M10" s="3">
         <v>34400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="N10" s="3">
         <v>28600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="O10" s="3">
         <v>18600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="P10" s="3">
         <v>7300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="Q10" s="3">
         <v>7300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="R10" s="3">
         <v>2800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="S10" s="3">
         <v>9900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="T10" s="3">
         <v>11700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="U10" s="3">
         <v>13600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="V10" s="3">
         <v>11400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="W10" s="3">
         <v>19700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="X10" s="3">
         <v>18400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="Y10" s="3">
         <v>24200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Z10" s="3">
         <v>24100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="AA10" s="3">
         <v>18600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AB10" s="3">
         <v>13000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AC10" s="3">
         <v>13900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AD10" s="3">
         <v>10200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AE10" s="3">
         <v>8900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AF10" s="3">
         <v>7600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AG10" s="3">
         <v>7900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AH10" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,8 +1123,11 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1173,8 +1215,17 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,31 +1313,40 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1300,20 +1360,20 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>500</v>
-      </c>
-      <c r="P14" s="3">
-        <v>400</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
+      <c r="R14" s="3">
+        <v>500</v>
+      </c>
+      <c r="S14" s="3">
+        <v>400</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
@@ -1324,14 +1384,14 @@
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1351,8 +1411,17 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1440,8 +1509,17 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1548,207 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>144500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>149900</v>
+      </c>
+      <c r="F17" s="3">
+        <v>146000</v>
+      </c>
+      <c r="G17" s="3">
         <v>157200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="H17" s="3">
         <v>168700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="I17" s="3">
         <v>176100</v>
       </c>
-      <c r="G17" s="3">
-        <v>639200</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
+        <v>161400</v>
+      </c>
+      <c r="K17" s="3">
         <v>169500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="L17" s="3">
         <v>160200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="M17" s="3">
         <v>148100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="N17" s="3">
         <v>128500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="O17" s="3">
         <v>118500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="P17" s="3">
         <v>94100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="Q17" s="3">
         <v>99600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="R17" s="3">
         <v>91000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="S17" s="3">
         <v>104200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="T17" s="3">
         <v>109100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="U17" s="3">
         <v>117700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="V17" s="3">
         <v>124900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="W17" s="3">
         <v>135700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="X17" s="3">
         <v>127800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Y17" s="3">
         <v>123100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Z17" s="3">
         <v>137500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="AA17" s="3">
         <v>120100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AB17" s="3">
         <v>106400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AC17" s="3">
         <v>108500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AD17" s="3">
         <v>103600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AE17" s="3">
         <v>95800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AF17" s="3">
         <v>89800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AG17" s="3">
         <v>86800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AH17" s="3">
         <v>83300</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F18" s="3">
+        <v>10400</v>
+      </c>
+      <c r="G18" s="3">
         <v>11400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="H18" s="3">
         <v>4700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="I18" s="3">
         <v>12400</v>
       </c>
-      <c r="G18" s="3">
-        <v>64800</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
+        <v>11100</v>
+      </c>
+      <c r="K18" s="3">
         <v>21100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="L18" s="3">
         <v>13200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="M18" s="3">
         <v>19400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="N18" s="3">
         <v>17000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="O18" s="3">
         <v>8500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="P18" s="3">
         <v>200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="Q18" s="3">
         <v>200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="R18" s="3">
         <v>-1900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="S18" s="3">
         <v>600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="T18" s="3">
         <v>3300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="U18" s="3">
         <v>4800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="V18" s="3">
         <v>5100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="W18" s="3">
         <v>10000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="X18" s="3">
         <v>8100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="Y18" s="3">
         <v>13900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Z18" s="3">
         <v>10300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="AA18" s="3">
         <v>7200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AB18" s="3">
         <v>4600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AC18" s="3">
         <v>5800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AD18" s="3">
         <v>3000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AE18" s="3">
         <v>2500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AF18" s="3">
         <v>1800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AG18" s="3">
         <v>1500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AH18" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,8 +1780,11 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1729,405 +1831,450 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="V20" s="3">
         <v>-200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="X20" s="3">
         <v>-300</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="AA20" s="3">
         <v>200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AB20" s="3">
         <v>400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AC20" s="3">
         <v>200</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AF20" s="3">
         <v>900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AG20" s="3">
         <v>500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AH20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>11700</v>
+      </c>
+      <c r="F21" s="3">
+        <v>14200</v>
+      </c>
+      <c r="G21" s="3">
         <v>14700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="H21" s="3">
         <v>8000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="I21" s="3">
         <v>15700</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
+        <v>15200</v>
+      </c>
+      <c r="K21" s="3">
         <v>24500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="L21" s="3">
         <v>20200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="M21" s="3">
         <v>9100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="N21" s="3">
         <v>20500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="O21" s="3">
         <v>11900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="P21" s="3">
         <v>3800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="Q21" s="3">
         <v>3800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="R21" s="3">
         <v>1700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="S21" s="3">
         <v>4000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="T21" s="3">
         <v>6900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="U21" s="3">
         <v>8300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="V21" s="3">
         <v>8400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="W21" s="3">
         <v>13300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="X21" s="3">
         <v>11200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="Y21" s="3">
         <v>17300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Z21" s="3">
         <v>13700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="AA21" s="3">
         <v>10500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AB21" s="3">
         <v>8000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AC21" s="3">
         <v>9100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AD21" s="3">
         <v>6100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AE21" s="3">
         <v>5600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AF21" s="3">
         <v>5600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AG21" s="3">
         <v>4900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AH21" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G22" s="3">
         <v>1600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="H22" s="3">
         <v>1700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="I22" s="3">
         <v>1500</v>
       </c>
-      <c r="G22" s="3">
-        <v>3300</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K22" s="3">
         <v>800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="L22" s="3">
         <v>700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="M22" s="3">
         <v>600</v>
-      </c>
-      <c r="K22" s="3">
-        <v>400</v>
-      </c>
-      <c r="L22" s="3">
-        <v>300</v>
-      </c>
-      <c r="M22" s="3">
-        <v>300</v>
       </c>
       <c r="N22" s="3">
         <v>400</v>
       </c>
       <c r="O22" s="3">
+        <v>300</v>
+      </c>
+      <c r="P22" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q22" s="3">
         <v>400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
+        <v>400</v>
+      </c>
+      <c r="S22" s="3">
         <v>700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="T22" s="3">
         <v>800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="U22" s="3">
         <v>900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="V22" s="3">
         <v>1000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="W22" s="3">
         <v>1200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="X22" s="3">
         <v>1300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="Y22" s="3">
         <v>1300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Z22" s="3">
         <v>1100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="AA22" s="3">
         <v>900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AB22" s="3">
         <v>800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AC22" s="3">
         <v>800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AD22" s="3">
         <v>600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AE22" s="3">
         <v>500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AF22" s="3">
         <v>600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AG22" s="3">
         <v>700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AH22" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F23" s="3">
+        <v>9200</v>
+      </c>
+      <c r="G23" s="3">
         <v>9800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="H23" s="3">
         <v>2900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="I23" s="3">
         <v>10900</v>
       </c>
-      <c r="G23" s="3">
-        <v>61500</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
+        <v>9900</v>
+      </c>
+      <c r="K23" s="3">
         <v>20300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="L23" s="3">
         <v>12600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="M23" s="3">
         <v>18800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="N23" s="3">
         <v>16700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="O23" s="3">
         <v>8200</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-200</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-2300</v>
       </c>
       <c r="P23" s="3">
         <v>-100</v>
       </c>
       <c r="Q23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="S23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T23" s="3">
         <v>2500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="U23" s="3">
         <v>3800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="V23" s="3">
         <v>4000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="W23" s="3">
         <v>8700</v>
-      </c>
-      <c r="U23" s="3">
-        <v>6500</v>
-      </c>
-      <c r="V23" s="3">
-        <v>12500</v>
-      </c>
-      <c r="W23" s="3">
-        <v>9200</v>
       </c>
       <c r="X23" s="3">
         <v>6500</v>
       </c>
       <c r="Y23" s="3">
+        <v>12500</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>6500</v>
+      </c>
+      <c r="AB23" s="3">
         <v>4200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AC23" s="3">
         <v>5200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AD23" s="3">
         <v>2400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AE23" s="3">
         <v>2200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AF23" s="3">
         <v>2000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AG23" s="3">
         <v>1300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AH23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F24" s="3">
+        <v>800</v>
+      </c>
+      <c r="G24" s="3">
         <v>3500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="H24" s="3">
         <v>-600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="I24" s="3">
         <v>2500</v>
       </c>
-      <c r="G24" s="3">
-        <v>13200</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K24" s="3">
         <v>4300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="L24" s="3">
         <v>3000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="M24" s="3">
         <v>4200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="N24" s="3">
         <v>3300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="O24" s="3">
         <v>1700</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>-1200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="S24" s="3">
         <v>-300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="T24" s="3">
         <v>500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="U24" s="3">
         <v>700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="V24" s="3">
         <v>-400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="W24" s="3">
         <v>2100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="X24" s="3">
         <v>1600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="Y24" s="3">
         <v>2800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Z24" s="3">
         <v>2400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="AA24" s="3">
         <v>1500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AB24" s="3">
         <v>-4200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AC24" s="3">
         <v>2200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AD24" s="3">
         <v>1000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AE24" s="3">
         <v>900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AF24" s="3">
         <v>-100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AG24" s="3">
         <v>600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AH24" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2362,213 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F26" s="3">
+        <v>8300</v>
+      </c>
+      <c r="G26" s="3">
         <v>6400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="H26" s="3">
         <v>3500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="I26" s="3">
         <v>8400</v>
       </c>
-      <c r="G26" s="3">
-        <v>48400</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
+        <v>8200</v>
+      </c>
+      <c r="K26" s="3">
         <v>16000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="L26" s="3">
         <v>9500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="M26" s="3">
         <v>14600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="N26" s="3">
         <v>13400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="O26" s="3">
         <v>6500</v>
       </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="R26" s="3">
         <v>-1100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="S26" s="3">
         <v>200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="T26" s="3">
         <v>2000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="U26" s="3">
         <v>3200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="V26" s="3">
         <v>4300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="W26" s="3">
         <v>6600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="X26" s="3">
         <v>4900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="Y26" s="3">
         <v>9800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Z26" s="3">
         <v>6800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="AA26" s="3">
         <v>5000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AB26" s="3">
         <v>8400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AC26" s="3">
         <v>3000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AD26" s="3">
         <v>1400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AE26" s="3">
         <v>1300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AF26" s="3">
         <v>2200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AG26" s="3">
         <v>700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AH26" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F27" s="3">
+        <v>8300</v>
+      </c>
+      <c r="G27" s="3">
         <v>6400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="H27" s="3">
         <v>3500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="I27" s="3">
         <v>8400</v>
       </c>
-      <c r="G27" s="3">
-        <v>48400</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
+        <v>8200</v>
+      </c>
+      <c r="K27" s="3">
         <v>16000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="L27" s="3">
         <v>9500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="M27" s="3">
         <v>14600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="N27" s="3">
         <v>13400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="O27" s="3">
         <v>6500</v>
       </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="R27" s="3">
         <v>-1100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="S27" s="3">
         <v>200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="T27" s="3">
         <v>2000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="U27" s="3">
         <v>3200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="V27" s="3">
         <v>4300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="W27" s="3">
         <v>6600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="X27" s="3">
         <v>4900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="Y27" s="3">
         <v>9800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Z27" s="3">
         <v>6800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="AA27" s="3">
         <v>5000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AB27" s="3">
         <v>8400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AC27" s="3">
         <v>3000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AD27" s="3">
         <v>1400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AE27" s="3">
         <v>1300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AF27" s="3">
         <v>2200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AG27" s="3">
         <v>700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AH27" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2656,17 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2754,17 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2852,17 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,8 +2950,17 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2797,138 +3007,156 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="V32" s="3">
         <v>200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="X32" s="3">
         <v>300</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="AA32" s="3">
         <v>-200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AB32" s="3">
         <v>-400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AC32" s="3">
         <v>-200</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AF32" s="3">
         <v>-900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AG32" s="3">
         <v>-500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AH32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F33" s="3">
+        <v>8300</v>
+      </c>
+      <c r="G33" s="3">
         <v>6400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="H33" s="3">
         <v>3500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="I33" s="3">
         <v>8400</v>
       </c>
-      <c r="G33" s="3">
-        <v>48400</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
+        <v>8200</v>
+      </c>
+      <c r="K33" s="3">
         <v>16000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="L33" s="3">
         <v>9500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="M33" s="3">
         <v>14600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="N33" s="3">
         <v>13400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="O33" s="3">
         <v>6500</v>
       </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="R33" s="3">
         <v>-1100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="S33" s="3">
         <v>200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="T33" s="3">
         <v>2000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="U33" s="3">
         <v>3200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="V33" s="3">
         <v>4300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="W33" s="3">
         <v>6600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="X33" s="3">
         <v>4900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="Y33" s="3">
         <v>9800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Z33" s="3">
         <v>6800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="AA33" s="3">
         <v>5000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AB33" s="3">
         <v>8400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AC33" s="3">
         <v>3000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AD33" s="3">
         <v>1400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AE33" s="3">
         <v>1300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AF33" s="3">
         <v>2200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AG33" s="3">
         <v>700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AH33" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3244,218 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F35" s="3">
+        <v>8300</v>
+      </c>
+      <c r="G35" s="3">
         <v>6400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="H35" s="3">
         <v>3500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="I35" s="3">
         <v>8400</v>
       </c>
-      <c r="G35" s="3">
-        <v>48400</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
+        <v>8200</v>
+      </c>
+      <c r="K35" s="3">
         <v>16000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="L35" s="3">
         <v>9500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="M35" s="3">
         <v>14600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="N35" s="3">
         <v>13400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="O35" s="3">
         <v>6500</v>
       </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="R35" s="3">
         <v>-1100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="S35" s="3">
         <v>200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="T35" s="3">
         <v>2000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="U35" s="3">
         <v>3200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="V35" s="3">
         <v>4300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="W35" s="3">
         <v>6600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="X35" s="3">
         <v>4900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="Y35" s="3">
         <v>9800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Z35" s="3">
         <v>6800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="AA35" s="3">
         <v>5000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AB35" s="3">
         <v>8400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AC35" s="3">
         <v>3000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AD35" s="3">
         <v>1400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AE35" s="3">
         <v>1300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AF35" s="3">
         <v>2200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AG35" s="3">
         <v>700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AH35" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45138</v>
+      </c>
+      <c r="G38" s="2">
         <v>45046</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>44957</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
         <v>44865</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>44773</v>
       </c>
-      <c r="H38" s="2">
+      <c r="K38" s="2">
         <v>44681</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>44592</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>44500</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>44408</v>
       </c>
-      <c r="L38" s="2">
+      <c r="O38" s="2">
         <v>44316</v>
       </c>
-      <c r="M38" s="2">
+      <c r="P38" s="2">
         <v>44227</v>
       </c>
-      <c r="N38" s="2">
+      <c r="Q38" s="2">
         <v>44135</v>
       </c>
-      <c r="O38" s="2">
+      <c r="R38" s="2">
         <v>44043</v>
       </c>
-      <c r="P38" s="2">
+      <c r="S38" s="2">
         <v>43951</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="T38" s="2">
         <v>43861</v>
       </c>
-      <c r="R38" s="2">
+      <c r="U38" s="2">
         <v>43769</v>
       </c>
-      <c r="S38" s="2">
+      <c r="V38" s="2">
         <v>43677</v>
       </c>
-      <c r="T38" s="2">
+      <c r="W38" s="2">
         <v>43585</v>
       </c>
-      <c r="U38" s="2">
+      <c r="X38" s="2">
         <v>43496</v>
       </c>
-      <c r="V38" s="2">
+      <c r="Y38" s="2">
         <v>43404</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Z38" s="2">
         <v>43312</v>
       </c>
-      <c r="X38" s="2">
+      <c r="AA38" s="2">
         <v>43220</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AB38" s="2">
         <v>43131</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AC38" s="2">
         <v>43039</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AD38" s="2">
         <v>42947</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AE38" s="2">
         <v>42855</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AF38" s="2">
         <v>42766</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AG38" s="2">
         <v>42674</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AH38" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3487,11 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,114 +3523,126 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F41" s="3">
+        <v>6200</v>
+      </c>
+      <c r="G41" s="3">
         <v>5100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="H41" s="3">
         <v>3700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="I41" s="3">
         <v>12800</v>
       </c>
-      <c r="G41" s="3">
-        <v>11800</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
+        <v>12700</v>
+      </c>
+      <c r="K41" s="3">
         <v>10900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="L41" s="3">
         <v>8800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="M41" s="3">
         <v>8400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="N41" s="3">
         <v>7100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="O41" s="3">
         <v>5400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="P41" s="3">
         <v>5400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="Q41" s="3">
         <v>6200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="R41" s="3">
         <v>4600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="S41" s="3">
         <v>11300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="T41" s="3">
         <v>3400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="U41" s="3">
         <v>6200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="V41" s="3">
         <v>7100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="W41" s="3">
         <v>6800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="X41" s="3">
         <v>4900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="Y41" s="3">
         <v>6200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Z41" s="3">
         <v>7100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="AA41" s="3">
         <v>4400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AB41" s="3">
         <v>6800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AC41" s="3">
         <v>6300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AD41" s="3">
         <v>7200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AE41" s="3">
         <v>8100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AF41" s="3">
         <v>8000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AG41" s="3">
         <v>8400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AH41" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E42" s="3">
+        <v>14800</v>
+      </c>
+      <c r="F42" s="3">
+        <v>15900</v>
+      </c>
+      <c r="G42" s="3">
         <v>14600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="H42" s="3">
         <v>10600</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>8</v>
@@ -3383,14 +3653,14 @@
       <c r="K42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="L42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -3443,364 +3713,409 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>73400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>73600</v>
+      </c>
+      <c r="F43" s="3">
+        <v>68500</v>
+      </c>
+      <c r="G43" s="3">
         <v>78200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="H43" s="3">
         <v>87000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="I43" s="3">
         <v>87400</v>
       </c>
-      <c r="G43" s="3">
-        <v>94100</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
+        <v>83700</v>
+      </c>
+      <c r="K43" s="3">
         <v>79500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="L43" s="3">
         <v>83700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="M43" s="3">
         <v>75200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="N43" s="3">
         <v>59900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="O43" s="3">
         <v>45000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="P43" s="3">
         <v>45000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="Q43" s="3">
         <v>48900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="R43" s="3">
         <v>41700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="S43" s="3">
         <v>47300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="T43" s="3">
         <v>54200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="U43" s="3">
         <v>55600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="V43" s="3">
         <v>59400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="W43" s="3">
         <v>67200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="X43" s="3">
         <v>64400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="Y43" s="3">
         <v>64700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Z43" s="3">
         <v>76500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="AA43" s="3">
         <v>68800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AB43" s="3">
         <v>55500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AC43" s="3">
         <v>54700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AD43" s="3">
         <v>53000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AE43" s="3">
         <v>49500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AF43" s="3">
         <v>43000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AG43" s="3">
         <v>39700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AH43" s="3">
         <v>39900</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>181300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>193400</v>
+      </c>
+      <c r="F44" s="3">
+        <v>208000</v>
+      </c>
+      <c r="G44" s="3">
         <v>208700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="H44" s="3">
         <v>219000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="I44" s="3">
         <v>234700</v>
       </c>
-      <c r="G44" s="3">
-        <v>225500</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
+        <v>244300</v>
+      </c>
+      <c r="K44" s="3">
         <v>232600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="L44" s="3">
         <v>203000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="M44" s="3">
         <v>149800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="N44" s="3">
         <v>121100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="O44" s="3">
         <v>114900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="P44" s="3">
         <v>114900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="Q44" s="3">
         <v>112500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="R44" s="3">
         <v>135800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="S44" s="3">
         <v>160200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="T44" s="3">
         <v>156300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="U44" s="3">
         <v>168800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="V44" s="3">
         <v>176400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="W44" s="3">
         <v>185800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="X44" s="3">
         <v>197900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="Y44" s="3">
         <v>198600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Z44" s="3">
         <v>170900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="AA44" s="3">
         <v>153700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AB44" s="3">
         <v>144900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AC44" s="3">
         <v>130700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AD44" s="3">
         <v>124500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AE44" s="3">
         <v>115200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AF44" s="3">
         <v>112600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AG44" s="3">
         <v>117000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AH44" s="3">
         <v>113400</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F45" s="3">
+        <v>2600</v>
+      </c>
+      <c r="G45" s="3">
         <v>3300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="H45" s="3">
         <v>15000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="I45" s="3">
         <v>13900</v>
       </c>
-      <c r="G45" s="3">
-        <v>7600</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
+        <v>11800</v>
+      </c>
+      <c r="K45" s="3">
         <v>8200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="L45" s="3">
         <v>8400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="M45" s="3">
         <v>7200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="N45" s="3">
         <v>6700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="O45" s="3">
         <v>2400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="P45" s="3">
         <v>2400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="Q45" s="3">
         <v>7400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="R45" s="3">
         <v>5600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="S45" s="3">
         <v>6700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="T45" s="3">
         <v>2000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="U45" s="3">
         <v>11800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="V45" s="3">
         <v>11600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="W45" s="3">
         <v>6700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="X45" s="3">
         <v>3700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="Y45" s="3">
         <v>5300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Z45" s="3">
         <v>7200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="AA45" s="3">
         <v>5700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AB45" s="3">
         <v>2900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AC45" s="3">
         <v>5900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AD45" s="3">
         <v>5500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AE45" s="3">
         <v>3400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AF45" s="3">
         <v>1200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AG45" s="3">
         <v>1700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AH45" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>277300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>292900</v>
+      </c>
+      <c r="F46" s="3">
+        <v>301100</v>
+      </c>
+      <c r="G46" s="3">
         <v>309900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="H46" s="3">
         <v>335300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
         <v>348800</v>
       </c>
-      <c r="G46" s="3">
-        <v>339000</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
+        <v>352600</v>
+      </c>
+      <c r="K46" s="3">
         <v>331100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="L46" s="3">
         <v>304000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="M46" s="3">
         <v>240600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="N46" s="3">
         <v>194800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="O46" s="3">
         <v>167700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="P46" s="3">
         <v>167700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="Q46" s="3">
         <v>175100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="R46" s="3">
         <v>187600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="S46" s="3">
         <v>225500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="T46" s="3">
         <v>215800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="U46" s="3">
         <v>242500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="V46" s="3">
         <v>254600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="W46" s="3">
         <v>266400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="X46" s="3">
         <v>270900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="Y46" s="3">
         <v>274800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Z46" s="3">
         <v>261700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="AA46" s="3">
         <v>232500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AB46" s="3">
         <v>210100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AC46" s="3">
         <v>197600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AD46" s="3">
         <v>190200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AE46" s="3">
         <v>176300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AF46" s="3">
         <v>164800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AG46" s="3">
         <v>166700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AH46" s="3">
         <v>169300</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3888,97 +4203,115 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>175800</v>
+      </c>
+      <c r="F48" s="3">
+        <v>169100</v>
+      </c>
+      <c r="G48" s="3">
         <v>160800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="H48" s="3">
         <v>158100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="I48" s="3">
         <v>151000</v>
       </c>
-      <c r="G48" s="3">
-        <v>141400</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
+        <v>145900</v>
+      </c>
+      <c r="K48" s="3">
         <v>140800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="L48" s="3">
         <v>137800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="M48" s="3">
         <v>137400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="N48" s="3">
         <v>135700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="O48" s="3">
         <v>139000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="P48" s="3">
         <v>139000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="Q48" s="3">
         <v>135400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="R48" s="3">
         <v>134600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="S48" s="3">
         <v>133400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="T48" s="3">
         <v>134700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="U48" s="3">
         <v>122800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="V48" s="3">
         <v>112500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="W48" s="3">
         <v>107900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="X48" s="3">
         <v>104700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="Y48" s="3">
         <v>105500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Z48" s="3">
         <v>104200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="AA48" s="3">
         <v>102500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AB48" s="3">
         <v>98100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AC48" s="3">
         <v>96100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AD48" s="3">
         <v>97200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AE48" s="3">
         <v>96900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AF48" s="3">
         <v>93700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AG48" s="3">
         <v>93200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AH48" s="3">
         <v>92600</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4066,8 +4399,17 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4497,17 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,97 +4595,115 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>13500</v>
+      </c>
+      <c r="F52" s="3">
+        <v>13400</v>
+      </c>
+      <c r="G52" s="3">
         <v>10900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="H52" s="3">
         <v>10200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="I52" s="3">
         <v>9300</v>
       </c>
-      <c r="G52" s="3">
-        <v>10600</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
+        <v>9700</v>
+      </c>
+      <c r="K52" s="3">
         <v>9500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="L52" s="3">
         <v>7200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="M52" s="3">
         <v>7200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="N52" s="3">
         <v>6200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="O52" s="3">
         <v>6100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="P52" s="3">
         <v>6100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="Q52" s="3">
         <v>6600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="R52" s="3">
         <v>5500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="S52" s="3">
         <v>4700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="T52" s="3">
         <v>4800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="U52" s="3">
         <v>3900</v>
-      </c>
-      <c r="S52" s="3">
-        <v>3900</v>
-      </c>
-      <c r="T52" s="3">
-        <v>4500</v>
-      </c>
-      <c r="U52" s="3">
-        <v>4300</v>
       </c>
       <c r="V52" s="3">
         <v>3900</v>
       </c>
       <c r="W52" s="3">
+        <v>4500</v>
+      </c>
+      <c r="X52" s="3">
+        <v>4300</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>3900</v>
+      </c>
+      <c r="Z52" s="3">
         <v>3600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="AA52" s="3">
         <v>6200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AB52" s="3">
         <v>5400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AC52" s="3">
         <v>4600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AD52" s="3">
         <v>4700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AE52" s="3">
         <v>2000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AF52" s="3">
         <v>2300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AG52" s="3">
         <v>1500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AH52" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4791,115 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>474800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>482200</v>
+      </c>
+      <c r="F54" s="3">
+        <v>483700</v>
+      </c>
+      <c r="G54" s="3">
         <v>481700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="H54" s="3">
         <v>503700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
         <v>509200</v>
       </c>
-      <c r="G54" s="3">
-        <v>490900</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
+        <v>508100</v>
+      </c>
+      <c r="K54" s="3">
         <v>481500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="L54" s="3">
         <v>449000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="M54" s="3">
         <v>385200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="N54" s="3">
         <v>336800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="O54" s="3">
         <v>312800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="P54" s="3">
         <v>312800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="Q54" s="3">
         <v>317000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="R54" s="3">
         <v>327700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="S54" s="3">
         <v>363500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="T54" s="3">
         <v>355300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="U54" s="3">
         <v>369200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="V54" s="3">
         <v>371000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="W54" s="3">
         <v>378900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="X54" s="3">
         <v>379900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="Y54" s="3">
         <v>384100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Z54" s="3">
         <v>369500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="AA54" s="3">
         <v>341200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AB54" s="3">
         <v>313600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AC54" s="3">
         <v>298200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AD54" s="3">
         <v>292200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AE54" s="3">
         <v>275200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AF54" s="3">
         <v>260800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AG54" s="3">
         <v>261400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AH54" s="3">
         <v>263200</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4931,11 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,55 +4967,58 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>29400</v>
+      </c>
+      <c r="F57" s="3">
+        <v>33500</v>
+      </c>
+      <c r="G57" s="3">
         <v>34200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="H57" s="3">
         <v>39000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="I57" s="3">
         <v>39200</v>
       </c>
-      <c r="G57" s="3">
-        <v>40800</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
+        <v>53300</v>
+      </c>
+      <c r="K57" s="3">
         <v>52800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="L57" s="3">
         <v>38500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="M57" s="3">
         <v>34600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="N57" s="3">
         <v>19000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="O57" s="3">
         <v>16400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="P57" s="3">
         <v>16400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="Q57" s="3">
         <v>8300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="R57" s="3">
         <v>14500</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>8</v>
@@ -4633,14 +5026,14 @@
       <c r="T57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
-      </c>
-      <c r="V57" s="3">
-        <v>0</v>
-      </c>
-      <c r="W57" s="3">
-        <v>0</v>
+      <c r="U57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X57" s="3">
         <v>0</v>
@@ -4666,325 +5059,361 @@
       <c r="AE57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>62300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>63400</v>
+      </c>
+      <c r="F58" s="3">
+        <v>69000</v>
+      </c>
+      <c r="G58" s="3">
         <v>82200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="H58" s="3">
         <v>106800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="I58" s="3">
         <v>117200</v>
       </c>
-      <c r="G58" s="3">
-        <v>111400</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
+        <v>114800</v>
+      </c>
+      <c r="K58" s="3">
         <v>113800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="L58" s="3">
         <v>104400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="M58" s="3">
         <v>59000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="N58" s="3">
         <v>32700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="O58" s="3">
         <v>21300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="P58" s="3">
         <v>21300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="Q58" s="3">
         <v>35400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="R58" s="3">
         <v>42000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="S58" s="3">
         <v>74500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="T58" s="3">
         <v>65800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="U58" s="3">
         <v>82500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="V58" s="3">
         <v>88600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="W58" s="3">
         <v>100600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="X58" s="3">
         <v>107100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="Y58" s="3">
         <v>111200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Z58" s="3">
         <v>110500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="AA58" s="3">
         <v>90700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AB58" s="3">
         <v>77800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AC58" s="3">
         <v>67000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AD58" s="3">
         <v>67900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AE58" s="3">
         <v>56800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AF58" s="3">
         <v>49100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AG58" s="3">
         <v>50200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AH58" s="3">
         <v>43400</v>
       </c>
     </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>40500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>42700</v>
+      </c>
+      <c r="F59" s="3">
+        <v>39600</v>
+      </c>
+      <c r="G59" s="3">
         <v>34900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="H59" s="3">
         <v>34800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="I59" s="3">
         <v>35500</v>
       </c>
-      <c r="G59" s="3">
-        <v>43400</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
+        <v>38100</v>
+      </c>
+      <c r="K59" s="3">
         <v>35200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="L59" s="3">
         <v>31900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="M59" s="3">
         <v>26900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="N59" s="3">
         <v>23500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="O59" s="3">
         <v>22000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="P59" s="3">
         <v>22000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="Q59" s="3">
         <v>21000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="R59" s="3">
         <v>19500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="S59" s="3">
         <v>40700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="T59" s="3">
         <v>39900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="U59" s="3">
         <v>41800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="V59" s="3">
         <v>46400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="W59" s="3">
         <v>46000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="X59" s="3">
         <v>48100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="Y59" s="3">
         <v>52500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Z59" s="3">
         <v>46700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="AA59" s="3">
         <v>45300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AB59" s="3">
         <v>36400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AC59" s="3">
         <v>35400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AD59" s="3">
         <v>31400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AE59" s="3">
         <v>29100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AF59" s="3">
         <v>26200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AG59" s="3">
         <v>29200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AH59" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>129200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>135500</v>
+      </c>
+      <c r="F60" s="3">
+        <v>142100</v>
+      </c>
+      <c r="G60" s="3">
         <v>151300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="H60" s="3">
         <v>180600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="I60" s="3">
         <v>192000</v>
       </c>
-      <c r="G60" s="3">
-        <v>195600</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
+        <v>206200</v>
+      </c>
+      <c r="K60" s="3">
         <v>201800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="L60" s="3">
         <v>174800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="M60" s="3">
         <v>120500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="N60" s="3">
         <v>75200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="O60" s="3">
         <v>59600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="P60" s="3">
         <v>59600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="Q60" s="3">
         <v>64700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="R60" s="3">
         <v>75900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="S60" s="3">
         <v>115200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="T60" s="3">
         <v>105700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="U60" s="3">
         <v>124400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="V60" s="3">
         <v>135000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="W60" s="3">
         <v>146600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="X60" s="3">
         <v>155200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="Y60" s="3">
         <v>163600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Z60" s="3">
         <v>157100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="AA60" s="3">
         <v>136000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AB60" s="3">
         <v>114200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AC60" s="3">
         <v>102400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AD60" s="3">
         <v>99200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AE60" s="3">
         <v>85900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AF60" s="3">
         <v>75300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AG60" s="3">
         <v>79300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AH60" s="3">
         <v>73500</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E61" s="3">
+        <v>20800</v>
+      </c>
+      <c r="F61" s="3">
+        <v>20800</v>
+      </c>
+      <c r="G61" s="3">
         <v>20500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="H61" s="3">
         <v>20500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="I61" s="3">
         <v>20500</v>
       </c>
-      <c r="G61" s="3">
-        <v>12700</v>
-      </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
+        <v>12600</v>
+      </c>
+      <c r="K61" s="3">
         <v>12800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="L61" s="3">
         <v>12900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="M61" s="3">
         <v>12900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="N61" s="3">
         <v>13100</v>
-      </c>
-      <c r="L61" s="3">
-        <v>13100</v>
-      </c>
-      <c r="M61" s="3">
-        <v>13100</v>
-      </c>
-      <c r="N61" s="3">
-        <v>13000</v>
       </c>
       <c r="O61" s="3">
         <v>13100</v>
       </c>
       <c r="P61" s="3">
+        <v>13100</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>13000</v>
+      </c>
+      <c r="R61" s="3">
+        <v>13100</v>
+      </c>
+      <c r="S61" s="3">
         <v>12000</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>12000</v>
-      </c>
-      <c r="R61" s="3">
-        <v>12000</v>
-      </c>
-      <c r="S61" s="3">
-        <v>12200</v>
       </c>
       <c r="T61" s="3">
         <v>12000</v>
@@ -4993,7 +5422,7 @@
         <v>12000</v>
       </c>
       <c r="V61" s="3">
-        <v>12000</v>
+        <v>12200</v>
       </c>
       <c r="W61" s="3">
         <v>12000</v>
@@ -5022,97 +5451,115 @@
       <c r="AE61" s="3">
         <v>12000</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>12000</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>12000</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>18100</v>
+      </c>
+      <c r="F62" s="3">
+        <v>18300</v>
+      </c>
+      <c r="G62" s="3">
         <v>17400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="H62" s="3">
         <v>17900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="I62" s="3">
         <v>16000</v>
       </c>
-      <c r="G62" s="3">
-        <v>18200</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>17100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
+        <v>17100</v>
+      </c>
+      <c r="L62" s="3">
         <v>18500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="M62" s="3">
         <v>20600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="N62" s="3">
         <v>23900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="O62" s="3">
         <v>22900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="P62" s="3">
         <v>22900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="Q62" s="3">
         <v>22700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="R62" s="3">
         <v>22200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="S62" s="3">
         <v>19000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="T62" s="3">
         <v>21000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="U62" s="3">
         <v>15100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="V62" s="3">
         <v>8700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="W62" s="3">
         <v>7200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="X62" s="3">
         <v>7200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="Y62" s="3">
         <v>8000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Z62" s="3">
         <v>8800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="AA62" s="3">
         <v>7600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AB62" s="3">
         <v>7100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AC62" s="3">
         <v>12300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AD62" s="3">
         <v>12800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AE62" s="3">
         <v>11100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AF62" s="3">
         <v>9100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AG62" s="3">
         <v>8300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AH62" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5647,17 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5745,17 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5843,115 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>166800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>174500</v>
+      </c>
+      <c r="F66" s="3">
+        <v>181200</v>
+      </c>
+      <c r="G66" s="3">
         <v>189200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="H66" s="3">
         <v>219000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="I66" s="3">
         <v>228400</v>
       </c>
-      <c r="G66" s="3">
-        <v>226400</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
+        <v>235900</v>
+      </c>
+      <c r="K66" s="3">
         <v>231700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="L66" s="3">
         <v>206200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="M66" s="3">
         <v>154100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="N66" s="3">
         <v>112200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="O66" s="3">
         <v>95700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="P66" s="3">
         <v>95700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="Q66" s="3">
         <v>100400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="R66" s="3">
         <v>111200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="S66" s="3">
         <v>146200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="T66" s="3">
         <v>138700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="U66" s="3">
         <v>151500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="V66" s="3">
         <v>155900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="W66" s="3">
         <v>165800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="X66" s="3">
         <v>174400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="Y66" s="3">
         <v>183700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Z66" s="3">
         <v>177900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="AA66" s="3">
         <v>155600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AB66" s="3">
         <v>133300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AC66" s="3">
         <v>126700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AD66" s="3">
         <v>124000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AE66" s="3">
         <v>109000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AF66" s="3">
         <v>96500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AG66" s="3">
         <v>99700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AH66" s="3">
         <v>102500</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5983,11 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +6075,17 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +6173,17 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +6271,17 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,79 +6369,88 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>255300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>255000</v>
+      </c>
+      <c r="F72" s="3">
+        <v>249900</v>
+      </c>
+      <c r="G72" s="3">
         <v>241600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="H72" s="3">
         <v>235600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="I72" s="3">
         <v>232100</v>
       </c>
-      <c r="G72" s="3">
-        <v>216200</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
+        <v>223800</v>
+      </c>
+      <c r="K72" s="3">
         <v>201300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="L72" s="3">
         <v>193800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="M72" s="3">
         <v>181000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="N72" s="3">
         <v>171700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="O72" s="3">
         <v>165400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="P72" s="3">
         <v>165400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="Q72" s="3">
         <v>165500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="R72" s="3">
         <v>165600</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W72" s="3">
         <v>213100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="X72" s="3">
         <v>205600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="Y72" s="3">
         <v>200500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Z72" s="3">
         <v>191500</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z72" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA72" s="3" t="s">
         <v>8</v>
@@ -5936,17 +6458,26 @@
       <c r="AB72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6565,17 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6663,17 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6761,115 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>308000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>307700</v>
+      </c>
+      <c r="F76" s="3">
+        <v>302500</v>
+      </c>
+      <c r="G76" s="3">
         <v>292500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="H76" s="3">
         <v>284700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
         <v>280700</v>
       </c>
-      <c r="G76" s="3">
-        <v>264500</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
+        <v>272300</v>
+      </c>
+      <c r="K76" s="3">
         <v>249800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="L76" s="3">
         <v>242800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="M76" s="3">
         <v>231100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="N76" s="3">
         <v>224600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="O76" s="3">
         <v>217100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="P76" s="3">
         <v>217100</v>
-      </c>
-      <c r="N76" s="3">
-        <v>216600</v>
-      </c>
-      <c r="O76" s="3">
-        <v>216500</v>
-      </c>
-      <c r="P76" s="3">
-        <v>217300</v>
       </c>
       <c r="Q76" s="3">
         <v>216600</v>
       </c>
       <c r="R76" s="3">
+        <v>216500</v>
+      </c>
+      <c r="S76" s="3">
+        <v>217300</v>
+      </c>
+      <c r="T76" s="3">
+        <v>216600</v>
+      </c>
+      <c r="U76" s="3">
         <v>217800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="V76" s="3">
         <v>215200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="W76" s="3">
         <v>213100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="X76" s="3">
         <v>205600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="Y76" s="3">
         <v>200500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Z76" s="3">
         <v>191500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="AA76" s="3">
         <v>185600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AB76" s="3">
         <v>180400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AC76" s="3">
         <v>171500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AD76" s="3">
         <v>168200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AE76" s="3">
         <v>166200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AF76" s="3">
         <v>164400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AG76" s="3">
         <v>161700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AH76" s="3">
         <v>160600</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6957,218 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45138</v>
+      </c>
+      <c r="G80" s="2">
         <v>45046</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>44957</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
         <v>44865</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>44773</v>
       </c>
-      <c r="H80" s="2">
+      <c r="K80" s="2">
         <v>44681</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>44592</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>44500</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>44408</v>
       </c>
-      <c r="L80" s="2">
+      <c r="O80" s="2">
         <v>44316</v>
       </c>
-      <c r="M80" s="2">
+      <c r="P80" s="2">
         <v>44227</v>
       </c>
-      <c r="N80" s="2">
+      <c r="Q80" s="2">
         <v>44135</v>
       </c>
-      <c r="O80" s="2">
+      <c r="R80" s="2">
         <v>44043</v>
       </c>
-      <c r="P80" s="2">
+      <c r="S80" s="2">
         <v>43951</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="T80" s="2">
         <v>43861</v>
       </c>
-      <c r="R80" s="2">
+      <c r="U80" s="2">
         <v>43769</v>
       </c>
-      <c r="S80" s="2">
+      <c r="V80" s="2">
         <v>43677</v>
       </c>
-      <c r="T80" s="2">
+      <c r="W80" s="2">
         <v>43585</v>
       </c>
-      <c r="U80" s="2">
+      <c r="X80" s="2">
         <v>43496</v>
       </c>
-      <c r="V80" s="2">
+      <c r="Y80" s="2">
         <v>43404</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Z80" s="2">
         <v>43312</v>
       </c>
-      <c r="X80" s="2">
+      <c r="AA80" s="2">
         <v>43220</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AB80" s="2">
         <v>43131</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AC80" s="2">
         <v>43039</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AD80" s="2">
         <v>42947</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AE80" s="2">
         <v>42855</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AF80" s="2">
         <v>42766</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AG80" s="2">
         <v>42674</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AH80" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F81" s="3">
+        <v>8300</v>
+      </c>
+      <c r="G81" s="3">
         <v>6400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="H81" s="3">
         <v>3500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="I81" s="3">
         <v>8400</v>
       </c>
-      <c r="G81" s="3">
-        <v>48400</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
+        <v>8200</v>
+      </c>
+      <c r="K81" s="3">
         <v>16000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="L81" s="3">
         <v>9500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="M81" s="3">
         <v>14600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="N81" s="3">
         <v>13400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="O81" s="3">
         <v>6500</v>
       </c>
-      <c r="M81" s="3">
-        <v>0</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="R81" s="3">
         <v>-1100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="S81" s="3">
         <v>200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="T81" s="3">
         <v>2000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="U81" s="3">
         <v>3200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="V81" s="3">
         <v>4300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="W81" s="3">
         <v>6600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="X81" s="3">
         <v>4900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="Y81" s="3">
         <v>9800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Z81" s="3">
         <v>6800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="AA81" s="3">
         <v>5000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AB81" s="3">
         <v>8400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AC81" s="3">
         <v>3000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AD81" s="3">
         <v>1400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AE81" s="3">
         <v>1300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AF81" s="3">
         <v>2200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AG81" s="3">
         <v>700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AH81" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,97 +7200,109 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F83" s="3">
+        <v>3700</v>
+      </c>
+      <c r="G83" s="3">
         <v>3300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="H83" s="3">
         <v>3300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="I83" s="3">
         <v>3300</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
+        <v>4100</v>
+      </c>
+      <c r="K83" s="3">
         <v>3500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="L83" s="3">
         <v>7000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="M83" s="3">
         <v>-10300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="N83" s="3">
         <v>3400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="O83" s="3">
         <v>3400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="P83" s="3">
         <v>3500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="Q83" s="3">
         <v>3600</v>
-      </c>
-      <c r="O83" s="3">
-        <v>3500</v>
-      </c>
-      <c r="P83" s="3">
-        <v>3400</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>3500</v>
       </c>
       <c r="R83" s="3">
         <v>3500</v>
       </c>
       <c r="S83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="T83" s="3">
         <v>3500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
+        <v>3500</v>
+      </c>
+      <c r="V83" s="3">
+        <v>3500</v>
+      </c>
+      <c r="W83" s="3">
         <v>3400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="X83" s="3">
         <v>3400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="Y83" s="3">
         <v>3400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Z83" s="3">
         <v>3300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="AA83" s="3">
         <v>3100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AB83" s="3">
         <v>3000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AC83" s="3">
         <v>3100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AD83" s="3">
         <v>3000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AE83" s="3">
         <v>2900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AF83" s="3">
         <v>2900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AG83" s="3">
         <v>2900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AH83" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +7390,17 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7488,17 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7586,17 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7684,17 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7782,115 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>18100</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-46100</v>
+      </c>
+      <c r="G89" s="3">
         <v>53200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="H89" s="3">
         <v>6700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
+        <v>9400</v>
+      </c>
+      <c r="K89" s="3">
         <v>5100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="L89" s="3">
         <v>-30200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="M89" s="3">
         <v>-54700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="N89" s="3">
         <v>-6300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="O89" s="3">
         <v>-4600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="P89" s="3">
         <v>21200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="Q89" s="3">
         <v>3600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="R89" s="3">
         <v>23600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="S89" s="3">
         <v>5000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="T89" s="3">
         <v>23000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="U89" s="3">
         <v>11100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="V89" s="3">
         <v>22600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="W89" s="3">
         <v>12900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="X89" s="3">
         <v>14800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="Y89" s="3">
         <v>1400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Z89" s="3">
         <v>-9500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="AA89" s="3">
         <v>-11800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AB89" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AC89" s="3">
         <v>2500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AD89" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AE89" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AF89" s="3">
         <v>7800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AG89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AH89" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,8 +7922,11 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7351,8 +8014,17 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +8112,17 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,8 +8210,17 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7561,32 +8251,32 @@
       <c r="L94" s="3">
         <v>0</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
+      <c r="M94" s="3">
+        <v>0</v>
       </c>
       <c r="N94" s="3">
-        <v>4100</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>8</v>
+      <c r="Q94" s="3">
+        <v>4100</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -7618,8 +8308,17 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +8350,11 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +8442,17 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8540,17 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8638,17 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,8 +8736,17 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8096,8 +8834,17 @@
       <c r="AE100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8185,8 +8932,17 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8272,6 +9028,15 @@
         <v>0</v>
       </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WEBC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WEBC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
   <si>
     <t>WEBC</t>
   </si>
@@ -656,442 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E7" s="2">
         <v>45322</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45230</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45138</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45046</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44957</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44865</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44773</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44681</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44592</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44500</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44408</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44316</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44227</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44135</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44043</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43951</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43861</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43769</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43677</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43585</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43496</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43404</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43312</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43220</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43131</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43039</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42947</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42855</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42766</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42674</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>153200</v>
+      </c>
+      <c r="E8" s="3">
         <v>146000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>157800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>156400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>168600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>173400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>188500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>172500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>190600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>173400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>167500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>145500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>127000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>94300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>99800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>89100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>104800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>112400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>122500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>130000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>145700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>135900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>137000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>147800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>127300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>111000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>114300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>106600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>98300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>91600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>88300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>84000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>133500</v>
+      </c>
+      <c r="E9" s="3">
         <v>133000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>136200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>131900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>145000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>158100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>162500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>151400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>157100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>144300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>133100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>116900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>108400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>87000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>92500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>86300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>94900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>100700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>108900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>118600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>126000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>117500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>112800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>123700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>108700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>98000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>100400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>96400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>89400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>84000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>80400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>77300</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E10" s="3">
         <v>13000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>21600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>24500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>23600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>15300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>26000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>21100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>33500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>29100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>34400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>28600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>18600</v>
-      </c>
-      <c r="P10" s="3">
-        <v>7300</v>
       </c>
       <c r="Q10" s="3">
         <v>7300</v>
       </c>
       <c r="R10" s="3">
+        <v>7300</v>
+      </c>
+      <c r="S10" s="3">
         <v>2800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>9900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>11700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>13600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>11400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>19700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>18400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>24200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>24100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>18600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>13000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>13900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>10200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>7600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>7900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1126,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1224,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1322,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1348,8 +1367,8 @@
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
@@ -1369,14 +1388,14 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>400</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
@@ -1393,8 +1412,8 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1420,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1518,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1551,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>146100</v>
+      </c>
+      <c r="E17" s="3">
         <v>144500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>149900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>146000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>157200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>168700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>176100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>161400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>169500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>160200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>148100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>128500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>118500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>94100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>99600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>91000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>104200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>109100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>117700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>124900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>135700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>127800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>123100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>137500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>120100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>106400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>108500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>103600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>95800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>89800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>86800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>83300</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E18" s="3">
         <v>1500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>10400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>11400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>12400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>11100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>21100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>13200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>19400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>17000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8500</v>
-      </c>
-      <c r="P18" s="3">
-        <v>200</v>
       </c>
       <c r="Q18" s="3">
         <v>200</v>
       </c>
       <c r="R18" s="3">
+        <v>200</v>
+      </c>
+      <c r="S18" s="3">
         <v>-1900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>5100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>10000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>8100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>13900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>10300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>7200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>5800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1783,8 +1815,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1840,441 +1873,456 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-300</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>200</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E21" s="3">
         <v>5300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>11700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>14200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>14700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>8000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>15700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>15200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>24500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>20200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>9100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>20500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>11900</v>
-      </c>
-      <c r="P21" s="3">
-        <v>3800</v>
       </c>
       <c r="Q21" s="3">
         <v>3800</v>
       </c>
       <c r="R21" s="3">
+        <v>3800</v>
+      </c>
+      <c r="S21" s="3">
         <v>1700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>6900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>8300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>8400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>13300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>11200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>17300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>13700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>10500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>8000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>9100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>6100</v>
-      </c>
-      <c r="AE21" s="3">
-        <v>5600</v>
       </c>
       <c r="AF21" s="3">
         <v>5600</v>
       </c>
       <c r="AG21" s="3">
+        <v>5600</v>
+      </c>
+      <c r="AH21" s="3">
         <v>4900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>700</v>
+      </c>
+      <c r="E22" s="3">
         <v>1100</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1300</v>
       </c>
       <c r="F22" s="3">
         <v>1300</v>
       </c>
       <c r="G22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H22" s="3">
         <v>1600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>400</v>
-      </c>
-      <c r="O22" s="3">
-        <v>300</v>
       </c>
       <c r="P22" s="3">
         <v>300</v>
       </c>
       <c r="Q22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="R22" s="3">
         <v>400</v>
       </c>
       <c r="S22" s="3">
+        <v>400</v>
+      </c>
+      <c r="T22" s="3">
         <v>700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1200</v>
-      </c>
-      <c r="X22" s="3">
-        <v>1300</v>
       </c>
       <c r="Y22" s="3">
         <v>1300</v>
       </c>
       <c r="Z22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AA22" s="3">
         <v>1100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>900</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>800</v>
       </c>
       <c r="AC22" s="3">
         <v>800</v>
       </c>
       <c r="AD22" s="3">
+        <v>800</v>
+      </c>
+      <c r="AE22" s="3">
         <v>600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>600</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>700</v>
       </c>
       <c r="AH22" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E23" s="3">
         <v>500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>9200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>9800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>10900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>20300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>12600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>18800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>16700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>8700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>12500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>9200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>6500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>5200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1700</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>-1200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2371,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E26" s="3">
         <v>300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>16000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>14600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>13400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6500</v>
       </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
       <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3">
         <v>-200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>6600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>9800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>6800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>5000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>8400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E27" s="3">
         <v>300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>8200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>16000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>9500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>14600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>13400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6500</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
       <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
         <v>-200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>6600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>9800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>6800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>5000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>8400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2665,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2763,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2861,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2959,8 +3025,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3016,147 +3085,153 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>300</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-200</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E33" s="3">
         <v>300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>16000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>9500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>14600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>13400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6500</v>
       </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
       <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3">
         <v>-200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>6600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>9800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>6800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>5000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>8400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3253,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E35" s="3">
         <v>300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>16000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>9500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>14600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>13400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6500</v>
       </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
       <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3">
         <v>-200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>6600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>9800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>6800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>5000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>8400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E38" s="2">
         <v>45322</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45230</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45138</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45046</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44957</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44865</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44773</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44681</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44592</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44500</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44408</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44316</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44227</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44135</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44043</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43951</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43861</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43769</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43677</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43585</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43496</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43404</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43312</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43220</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43131</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43039</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42947</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42855</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42766</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42674</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3490,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3526,126 +3611,130 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E41" s="3">
         <v>3000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>12700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>10900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7100</v>
-      </c>
-      <c r="O41" s="3">
-        <v>5400</v>
       </c>
       <c r="P41" s="3">
         <v>5400</v>
       </c>
       <c r="Q41" s="3">
+        <v>5400</v>
+      </c>
+      <c r="R41" s="3">
         <v>6200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>11300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>7200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>8100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>8000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>8400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>14800</v>
+        <v>15400</v>
       </c>
       <c r="E42" s="3">
         <v>14800</v>
       </c>
       <c r="F42" s="3">
+        <v>14800</v>
+      </c>
+      <c r="G42" s="3">
         <v>15900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>14600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>10600</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>8</v>
@@ -3662,8 +3751,8 @@
       <c r="N42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -3722,400 +3811,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>70100</v>
+      </c>
+      <c r="E43" s="3">
         <v>73400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>73600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>68500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>78200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>87000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>87400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>83700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>79500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>83700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>75200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>59900</v>
-      </c>
-      <c r="O43" s="3">
-        <v>45000</v>
       </c>
       <c r="P43" s="3">
         <v>45000</v>
       </c>
       <c r="Q43" s="3">
+        <v>45000</v>
+      </c>
+      <c r="R43" s="3">
         <v>48900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>41700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>47300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>54200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>55600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>59400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>67200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>64400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>64700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>76500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>68800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>55500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>54700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>53000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>49500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>43000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>39700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>39900</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>174900</v>
+      </c>
+      <c r="E44" s="3">
         <v>181300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>193400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>208000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>208700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>219000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>234700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>244300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>232600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>203000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>149800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>121100</v>
-      </c>
-      <c r="O44" s="3">
-        <v>114900</v>
       </c>
       <c r="P44" s="3">
         <v>114900</v>
       </c>
       <c r="Q44" s="3">
+        <v>114900</v>
+      </c>
+      <c r="R44" s="3">
         <v>112500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>135800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>160200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>156300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>168800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>176400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>185800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>197900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>198600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>170900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>153700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>144900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>130700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>124500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>115200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>112600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>117000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>113400</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E45" s="3">
         <v>4800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>15000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>11800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6700</v>
-      </c>
-      <c r="O45" s="3">
-        <v>2400</v>
       </c>
       <c r="P45" s="3">
         <v>2400</v>
       </c>
       <c r="Q45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="R45" s="3">
         <v>7400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>11800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>11600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>5300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>7200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>5700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>5900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>5500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>269600</v>
+      </c>
+      <c r="E46" s="3">
         <v>277300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>292900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>301100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>309900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>335300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>348800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>352600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>331100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>304000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>240600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>194800</v>
-      </c>
-      <c r="O46" s="3">
-        <v>167700</v>
       </c>
       <c r="P46" s="3">
         <v>167700</v>
       </c>
       <c r="Q46" s="3">
+        <v>167700</v>
+      </c>
+      <c r="R46" s="3">
         <v>175100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>187600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>225500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>215800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>242500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>254600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>266400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>270900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>274800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>261700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>232500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>210100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>197600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>190200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>176300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>164800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>166700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>169300</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4212,106 +4316,112 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>184000</v>
+      </c>
+      <c r="E48" s="3">
         <v>182000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>175800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>169100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>160800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>158100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>151000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>145900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>140800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>137800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>137400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>135700</v>
-      </c>
-      <c r="O48" s="3">
-        <v>139000</v>
       </c>
       <c r="P48" s="3">
         <v>139000</v>
       </c>
       <c r="Q48" s="3">
+        <v>139000</v>
+      </c>
+      <c r="R48" s="3">
         <v>135400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>134600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>133400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>134700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>122800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>112500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>107900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>104700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>105500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>104200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>102500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>98100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>96100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>97200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>96900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>93700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>93200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>92600</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4408,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4506,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4604,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E52" s="3">
         <v>15600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>13400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9500</v>
-      </c>
-      <c r="L52" s="3">
-        <v>7200</v>
       </c>
       <c r="M52" s="3">
         <v>7200</v>
       </c>
       <c r="N52" s="3">
+        <v>7200</v>
+      </c>
+      <c r="O52" s="3">
         <v>6200</v>
-      </c>
-      <c r="O52" s="3">
-        <v>6100</v>
       </c>
       <c r="P52" s="3">
         <v>6100</v>
       </c>
       <c r="Q52" s="3">
+        <v>6100</v>
+      </c>
+      <c r="R52" s="3">
         <v>6600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4800</v>
-      </c>
-      <c r="U52" s="3">
-        <v>3900</v>
       </c>
       <c r="V52" s="3">
         <v>3900</v>
       </c>
       <c r="W52" s="3">
+        <v>3900</v>
+      </c>
+      <c r="X52" s="3">
         <v>4500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>4600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>4700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4800,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>470300</v>
+      </c>
+      <c r="E54" s="3">
         <v>474800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>482200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>483700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>481700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>503700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>509200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>508100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>481500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>449000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>385200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>336800</v>
-      </c>
-      <c r="O54" s="3">
-        <v>312800</v>
       </c>
       <c r="P54" s="3">
         <v>312800</v>
       </c>
       <c r="Q54" s="3">
+        <v>312800</v>
+      </c>
+      <c r="R54" s="3">
         <v>317000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>327700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>363500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>355300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>369200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>371000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>378900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>379900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>384100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>369500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>341200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>313600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>298200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>292200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>275200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>260800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>261400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>263200</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4934,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4970,58 +5099,59 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E57" s="3">
         <v>26300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>29400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>33500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>34200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>39000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>39200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>53300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>52800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>38500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>34600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>19000</v>
-      </c>
-      <c r="O57" s="3">
-        <v>16400</v>
       </c>
       <c r="P57" s="3">
         <v>16400</v>
       </c>
       <c r="Q57" s="3">
+        <v>16400</v>
+      </c>
+      <c r="R57" s="3">
         <v>8300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>14500</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>8</v>
@@ -5035,8 +5165,8 @@
       <c r="W57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X57" s="3">
-        <v>0</v>
+      <c r="X57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y57" s="3">
         <v>0</v>
@@ -5068,307 +5198,319 @@
       <c r="AH57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>47100</v>
+      </c>
+      <c r="E58" s="3">
         <v>62300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>63400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>69000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>82200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>106800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>117200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>114800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>113800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>104400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>59000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>32700</v>
-      </c>
-      <c r="O58" s="3">
-        <v>21300</v>
       </c>
       <c r="P58" s="3">
         <v>21300</v>
       </c>
       <c r="Q58" s="3">
+        <v>21300</v>
+      </c>
+      <c r="R58" s="3">
         <v>35400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>42000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>74500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>65800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>82500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>88600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>100600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>107100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>111200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>110500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>90700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>77800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>67000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>67900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>56800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>49100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>50200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>43400</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E59" s="3">
         <v>40500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>42700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>39600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>34900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>34800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>35500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>38100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>35200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>31900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>26900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>23500</v>
-      </c>
-      <c r="O59" s="3">
-        <v>22000</v>
       </c>
       <c r="P59" s="3">
         <v>22000</v>
       </c>
       <c r="Q59" s="3">
+        <v>22000</v>
+      </c>
+      <c r="R59" s="3">
         <v>21000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>19500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>40700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>39900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>41800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>46400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>46000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>48100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>52500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>46700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>45300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>36400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>35400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>31400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>29100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>26200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>29200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>118500</v>
+      </c>
+      <c r="E60" s="3">
         <v>129200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>135500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>142100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>151300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>180600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>192000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>206200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>201800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>174800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>120500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>75200</v>
-      </c>
-      <c r="O60" s="3">
-        <v>59600</v>
       </c>
       <c r="P60" s="3">
         <v>59600</v>
       </c>
       <c r="Q60" s="3">
+        <v>59600</v>
+      </c>
+      <c r="R60" s="3">
         <v>64700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>75900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>115200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>105700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>124400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>135000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>146600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>155200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>163600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>157100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>136000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>114200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>102400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>99200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>85900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>75300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>79300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>73500</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>20800</v>
+        <v>20700</v>
       </c>
       <c r="E61" s="3">
         <v>20800</v>
@@ -5377,7 +5519,7 @@
         <v>20800</v>
       </c>
       <c r="G61" s="3">
-        <v>20500</v>
+        <v>20800</v>
       </c>
       <c r="H61" s="3">
         <v>20500</v>
@@ -5386,19 +5528,19 @@
         <v>20500</v>
       </c>
       <c r="J61" s="3">
+        <v>20500</v>
+      </c>
+      <c r="K61" s="3">
         <v>12600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12800</v>
-      </c>
-      <c r="L61" s="3">
-        <v>12900</v>
       </c>
       <c r="M61" s="3">
         <v>12900</v>
       </c>
       <c r="N61" s="3">
-        <v>13100</v>
+        <v>12900</v>
       </c>
       <c r="O61" s="3">
         <v>13100</v>
@@ -5407,13 +5549,13 @@
         <v>13100</v>
       </c>
       <c r="Q61" s="3">
+        <v>13100</v>
+      </c>
+      <c r="R61" s="3">
         <v>13000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>13100</v>
-      </c>
-      <c r="S61" s="3">
-        <v>12000</v>
       </c>
       <c r="T61" s="3">
         <v>12000</v>
@@ -5422,10 +5564,10 @@
         <v>12000</v>
       </c>
       <c r="V61" s="3">
+        <v>12000</v>
+      </c>
+      <c r="W61" s="3">
         <v>12200</v>
-      </c>
-      <c r="W61" s="3">
-        <v>12000</v>
       </c>
       <c r="X61" s="3">
         <v>12000</v>
@@ -5460,106 +5602,112 @@
       <c r="AH61" s="3">
         <v>12000</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E62" s="3">
         <v>16900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>18100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>18300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>17400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>17900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>16000</v>
-      </c>
-      <c r="J62" s="3">
-        <v>17100</v>
       </c>
       <c r="K62" s="3">
         <v>17100</v>
       </c>
       <c r="L62" s="3">
+        <v>17100</v>
+      </c>
+      <c r="M62" s="3">
         <v>18500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>20600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>23900</v>
-      </c>
-      <c r="O62" s="3">
-        <v>22900</v>
       </c>
       <c r="P62" s="3">
         <v>22900</v>
       </c>
       <c r="Q62" s="3">
+        <v>22900</v>
+      </c>
+      <c r="R62" s="3">
         <v>22700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>22200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>19000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>21000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>15100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8700</v>
-      </c>
-      <c r="W62" s="3">
-        <v>7200</v>
       </c>
       <c r="X62" s="3">
         <v>7200</v>
       </c>
       <c r="Y62" s="3">
+        <v>7200</v>
+      </c>
+      <c r="Z62" s="3">
         <v>8000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>7600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>7100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>12300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>12800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>11100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>9100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>8300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5656,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5754,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5852,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>154900</v>
+      </c>
+      <c r="E66" s="3">
         <v>166800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>174500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>181200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>189200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>219000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>228400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>235900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>231700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>206200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>154100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>112200</v>
-      </c>
-      <c r="O66" s="3">
-        <v>95700</v>
       </c>
       <c r="P66" s="3">
         <v>95700</v>
       </c>
       <c r="Q66" s="3">
+        <v>95700</v>
+      </c>
+      <c r="R66" s="3">
         <v>100400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>111200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>146200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>138700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>151500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>155900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>165800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>174400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>183700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>177900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>155600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>133300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>126700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>124000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>109000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>96500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>99700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>102500</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5986,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6084,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6182,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6280,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6378,8 +6548,11 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6387,49 +6560,49 @@
         <v>255300</v>
       </c>
       <c r="E72" s="3">
+        <v>255300</v>
+      </c>
+      <c r="F72" s="3">
         <v>255000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>249900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>241600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>235600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>232100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>223800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>201300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>193800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>181000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>171700</v>
-      </c>
-      <c r="O72" s="3">
-        <v>165400</v>
       </c>
       <c r="P72" s="3">
         <v>165400</v>
       </c>
       <c r="Q72" s="3">
+        <v>165400</v>
+      </c>
+      <c r="R72" s="3">
         <v>165500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>165600</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>8</v>
@@ -6440,20 +6613,20 @@
       <c r="V72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X72" s="3">
         <v>213100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>205600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>200500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>191500</v>
-      </c>
-      <c r="AA72" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB72" s="3" t="s">
         <v>8</v>
@@ -6467,8 +6640,8 @@
       <c r="AE72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF72" s="3">
-        <v>0</v>
+      <c r="AF72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG72" s="3">
         <v>0</v>
@@ -6476,8 +6649,11 @@
       <c r="AH72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6574,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6672,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6770,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>315400</v>
+      </c>
+      <c r="E76" s="3">
         <v>308000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>307700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>302500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>292500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>284700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>280700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>272300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>249800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>242800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>231100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>224600</v>
-      </c>
-      <c r="O76" s="3">
-        <v>217100</v>
       </c>
       <c r="P76" s="3">
         <v>217100</v>
       </c>
       <c r="Q76" s="3">
+        <v>217100</v>
+      </c>
+      <c r="R76" s="3">
         <v>216600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>216500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>217300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>216600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>217800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>215200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>213100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>205600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>200500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>191500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>185600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>180400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>171500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>168200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>166200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>164400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>161700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>160600</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6966,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E80" s="2">
         <v>45322</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45230</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45138</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45046</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44957</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44865</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44773</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44681</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44592</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44500</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44408</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44316</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44227</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44135</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44043</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43951</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43861</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43769</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43677</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43585</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43496</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43404</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43312</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43220</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43131</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43039</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42947</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42855</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42766</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42674</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E81" s="3">
         <v>300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>16000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>9500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>14600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>13400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6500</v>
       </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
       <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3">
         <v>-200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>6600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>9800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>6800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>5000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>8400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7203,13 +7400,14 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3700</v>
+        <v>3900</v>
       </c>
       <c r="E83" s="3">
         <v>3700</v>
@@ -7218,7 +7416,7 @@
         <v>3700</v>
       </c>
       <c r="G83" s="3">
-        <v>3300</v>
+        <v>3700</v>
       </c>
       <c r="H83" s="3">
         <v>3300</v>
@@ -7227,37 +7425,37 @@
         <v>3300</v>
       </c>
       <c r="J83" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K83" s="3">
         <v>4100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>-10300</v>
-      </c>
-      <c r="N83" s="3">
-        <v>3400</v>
       </c>
       <c r="O83" s="3">
         <v>3400</v>
       </c>
       <c r="P83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="Q83" s="3">
         <v>3500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3400</v>
-      </c>
-      <c r="T83" s="3">
-        <v>3500</v>
       </c>
       <c r="U83" s="3">
         <v>3500</v>
@@ -7266,7 +7464,7 @@
         <v>3500</v>
       </c>
       <c r="W83" s="3">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="X83" s="3">
         <v>3400</v>
@@ -7275,22 +7473,22 @@
         <v>3400</v>
       </c>
       <c r="Z83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="AA83" s="3">
         <v>3300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>3100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>3000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>3100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>3000</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>2900</v>
       </c>
       <c r="AF83" s="3">
         <v>2900</v>
@@ -7299,10 +7497,13 @@
         <v>2900</v>
       </c>
       <c r="AH83" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AI83" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7399,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7497,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7595,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7693,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7791,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E89" s="3">
         <v>9700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>18100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-46100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>53200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>9400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-30200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-54700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-6300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>21200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>23600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>5000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>23000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>11100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>22600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>12900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>14800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-9500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-11800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>7800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7925,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8023,8 +8243,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8121,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8219,8 +8445,11 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8260,14 +8489,14 @@
       <c r="O94" s="3">
         <v>0</v>
       </c>
-      <c r="P94" s="3" t="s">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>4100</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>8</v>
@@ -8278,8 +8507,8 @@
       <c r="U94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
@@ -8317,8 +8546,11 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8353,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8451,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8549,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8647,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8745,8 +8987,11 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8843,8 +9088,11 @@
       <c r="AH100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8941,8 +9189,11 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9037,6 +9288,9 @@
         <v>0</v>
       </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WEBC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WEBC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
   <si>
     <t>WEBC</t>
   </si>
@@ -656,454 +656,480 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45504</v>
+      </c>
+      <c r="F7" s="2">
         <v>45412</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45322</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45230</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45138</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45046</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44957</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44865</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44773</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44681</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44592</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44500</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44408</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44316</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44227</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44135</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44043</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43951</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43861</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43769</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43677</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43585</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43496</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43404</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43312</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43220</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43131</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43039</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42947</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42855</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42766</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42674</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>141400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>151400</v>
+      </c>
+      <c r="F8" s="3">
         <v>153200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>146000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>157800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>156400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>168600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>173400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>188500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>172500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>190600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>173400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>167500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>145500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>127000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>94300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>99800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>89100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>104800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>112400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>122500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>130000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>145700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>135900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>137000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>147800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>127300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>111000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>114300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>106600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>98300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>91600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>88300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>84000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>127700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>133800</v>
+      </c>
+      <c r="F9" s="3">
         <v>133500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>133000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>136200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>131900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>145000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>158100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>162500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>151400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>157100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>144300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>133100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>116900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>108400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>87000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>92500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>86300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>94900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>100700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>108900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>118600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>126000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>117500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>112800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>123700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>108700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>98000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>100400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>96400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>89400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>84000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>80400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>77300</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>17600</v>
+      </c>
+      <c r="F10" s="3">
         <v>19700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>13000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>21600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>24500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>23600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>15300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>26000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>21100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>33500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>29100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>34400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>28600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>18600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>7300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>7300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>2800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>9900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>11700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>13600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>11400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>19700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>18400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>24200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>24100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>18600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>13000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>13900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>10200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>8900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>7600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>7900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1165,10 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1268,14 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,40 +1375,46 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
@@ -1391,18 +1431,18 @@
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
         <v>500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>400</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1415,11 +1455,11 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1442,31 +1482,37 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>4700</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1543,8 +1589,14 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1629,224 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>140300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>147100</v>
+      </c>
+      <c r="F17" s="3">
         <v>146100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>144500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>149900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>146000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>157200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>168700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>176100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>161400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>169500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>160200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>148100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>128500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>118500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>94100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>99600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>91000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>104200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>109100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>117700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>124900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>135700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>127800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>123100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>137500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>120100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>106400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>108500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>103600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>95800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>89800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>86800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>83300</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F18" s="3">
         <v>7100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>1500</v>
       </c>
-      <c r="F18" s="3">
-        <v>7900</v>
-      </c>
-      <c r="G18" s="3">
-        <v>10400</v>
-      </c>
       <c r="H18" s="3">
+        <v>8000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>10500</v>
+      </c>
+      <c r="J18" s="3">
         <v>11400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>4700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>12400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>11100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>21100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>13200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>19400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>17000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>8500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-1900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>3300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>4800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>5100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>10000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>8100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>13900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>10300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>7200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>4600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>5800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>3000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>2500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>1800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>1500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,16 +1882,18 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1833,8 +1901,8 @@
       <c r="G20" s="3">
         <v>0</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
@@ -1876,352 +1944,376 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W20" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="X20" s="3">
         <v>-100</v>
       </c>
       <c r="Y20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-300</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>100</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>200</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>400</v>
       </c>
       <c r="AD20" s="3">
         <v>200</v>
       </c>
       <c r="AE20" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AF20" s="3">
         <v>200</v>
       </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI20" s="3">
         <v>900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>8600</v>
+      </c>
+      <c r="F21" s="3">
         <v>11000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>5300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>11700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>14200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>14700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>8000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>15700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>15200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>24500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>20200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>9100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>20500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>11900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>3800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>3800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>1700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>4000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>6900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>8300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>8400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>13300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>11200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>17300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>13700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>10500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>8000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>9100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>6100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>5600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>5600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>4900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F22" s="3">
         <v>700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>1100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>1300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>1300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>1600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>1700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>1500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>1200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>1000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>1200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>1300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>1300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>1100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>800</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>600</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>500</v>
       </c>
       <c r="AG22" s="3">
         <v>600</v>
       </c>
       <c r="AH22" s="3">
+        <v>500</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>600</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F23" s="3">
         <v>6400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>6700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>9200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>9800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>2900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>10900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>9900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>20300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>12600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>18800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>16700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>8200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-2300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>2500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>3800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>4000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>8700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>6500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>12500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>9200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>6500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>4200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>5200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>2400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>2200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>2000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>1300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2229,100 +2321,106 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>1600</v>
       </c>
-      <c r="G24" s="3">
-        <v>800</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J24" s="3">
         <v>3500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>2500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>1700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>4300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>3000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>4200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>3300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>1700</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>-1200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>2100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>1600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>2800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>2400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>1500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>2200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>1000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>-100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2520,228 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F26" s="3">
         <v>6400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>5100</v>
       </c>
-      <c r="G26" s="3">
-        <v>8300</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
+        <v>7300</v>
+      </c>
+      <c r="J26" s="3">
         <v>6400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>3500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>8400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>8200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>16000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>9500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>14600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>13400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>6500</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3">
         <v>-200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-1100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>2000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>3200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>4300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>6600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>4900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>9800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>6800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>5000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>8400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>3000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>1400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>1300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>2200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F27" s="3">
         <v>6400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>5100</v>
       </c>
-      <c r="G27" s="3">
-        <v>8300</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
+        <v>7300</v>
+      </c>
+      <c r="J27" s="3">
         <v>6400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>3500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>8400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>8200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>16000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>9500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>14600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>13400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>6500</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3">
         <v>-200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-1100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>2000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>3200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>4300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>6600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>4900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>9800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>6800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>5000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>8400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>3000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>1400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>1300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>2200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2841,14 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2948,14 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +3055,14 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,16 +3162,22 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -3045,8 +3185,8 @@
       <c r="G32" s="3">
         <v>0</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
@@ -3088,150 +3228,162 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W32" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="X32" s="3">
         <v>100</v>
       </c>
       <c r="Y32" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA32" s="3">
         <v>300</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-100</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-400</v>
       </c>
       <c r="AD32" s="3">
         <v>-200</v>
       </c>
       <c r="AE32" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="AF32" s="3">
         <v>-200</v>
       </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F33" s="3">
         <v>6400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>5100</v>
       </c>
-      <c r="G33" s="3">
-        <v>8300</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
+        <v>7300</v>
+      </c>
+      <c r="J33" s="3">
         <v>6400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>3500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>8400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>8200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>16000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>9500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>14600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>13400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>6500</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3">
         <v>-200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-1100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>2000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>3200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>4300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>6600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>4900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>9800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>6800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>5000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>8400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>3000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>1400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>1300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>2200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3483,233 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F35" s="3">
         <v>6400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>5100</v>
       </c>
-      <c r="G35" s="3">
-        <v>8300</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
+        <v>7300</v>
+      </c>
+      <c r="J35" s="3">
         <v>6400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>3500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>8400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>8200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>16000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>9500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>14600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>13400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>6500</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3">
         <v>-200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-1100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>2000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>3200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>4300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>6600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>4900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>9800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>6800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>5000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>8400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>3000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>1400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>1300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>2200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45504</v>
+      </c>
+      <c r="F38" s="2">
         <v>45412</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45322</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45230</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45138</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45046</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44957</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44865</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44773</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44681</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44592</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44500</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44408</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44316</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44227</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44135</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44043</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43951</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43861</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43769</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43677</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43585</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43496</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43404</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43312</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43220</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43131</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43039</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42947</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42855</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42766</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42674</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3745,10 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,136 +3784,144 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F41" s="3">
         <v>4400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>7000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>6200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>5100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>3700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>12800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>12700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>10900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>8800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>8400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>7100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>5400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>5400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>6200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>4600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>11300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>3400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>6200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>7100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>6800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>4900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>6200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>7100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>4400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>6800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>6300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>7200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>8100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>8000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>8400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E42" s="3">
+        <v>15900</v>
+      </c>
+      <c r="F42" s="3">
         <v>15400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>14800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>14800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>15900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>14600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>10600</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>8</v>
       </c>
@@ -3754,11 +3934,11 @@
       <c r="O42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -3814,435 +3994,465 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>58700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>70200</v>
+      </c>
+      <c r="F43" s="3">
         <v>70100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>73400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>73600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>68500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>78200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>87000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>87400</v>
-      </c>
-      <c r="K43" s="3">
-        <v>83700</v>
-      </c>
-      <c r="L43" s="3">
-        <v>79500</v>
       </c>
       <c r="M43" s="3">
         <v>83700</v>
       </c>
       <c r="N43" s="3">
+        <v>79500</v>
+      </c>
+      <c r="O43" s="3">
+        <v>83700</v>
+      </c>
+      <c r="P43" s="3">
         <v>75200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>59900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>45000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>45000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>48900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>41700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>47300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>54200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>55600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>59400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>67200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>64400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>64700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>76500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>68800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>55500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>54700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>53000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>49500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>43000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>39700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>39900</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>174700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>169500</v>
+      </c>
+      <c r="F44" s="3">
         <v>174900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>181300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>193400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>208000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>208700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>219000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>234700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>244300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>232600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>203000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>149800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>121100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>114900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>114900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>112500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>135800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>160200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>156300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>168800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>176400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>185800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>197900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>198600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>170900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>153700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>144900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>130700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>124500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>115200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>112600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>117000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>113400</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4900</v>
-      </c>
-      <c r="E45" s="3">
-        <v>4800</v>
-      </c>
-      <c r="F45" s="3">
-        <v>4100</v>
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G45" s="3">
-        <v>2600</v>
-      </c>
-      <c r="H45" s="3">
-        <v>3300</v>
-      </c>
-      <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
         <v>15000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>13900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>11800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>8200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>8400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>7200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>6700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>2400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>2400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>7400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>5600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>6700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>2000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>11800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>11600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>6700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>3700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>5300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>7200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>5700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>2900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>5900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>5500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>3400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>1200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>1700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>261200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>266400</v>
+      </c>
+      <c r="F46" s="3">
         <v>269600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>277300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>292900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>301100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>309900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>335300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>348800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>352600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>331100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>304000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>240600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>194800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>167700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>167700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>175100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>187600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>225500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>215800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>242500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>254600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>266400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>270900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>274800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>261700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>232500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>210100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>197600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>190200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>176300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>164800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>166700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>169300</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4319,109 +4529,121 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>191600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>191100</v>
+      </c>
+      <c r="F48" s="3">
         <v>184000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>182000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>175800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>169100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>160800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>158100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>151000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>145900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>140800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>137800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>137400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>135700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>139000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>139000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>135400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>134600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>133400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>134700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>122800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>112500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>107900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>104700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>105500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>104200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>102500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>98100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>96100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>97200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>96900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>93700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>93200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>92600</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4521,8 +4743,14 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4850,14 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4957,121 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>16700</v>
+        <v>15700</v>
       </c>
       <c r="E52" s="3">
         <v>15600</v>
       </c>
       <c r="F52" s="3">
+        <v>16700</v>
+      </c>
+      <c r="G52" s="3">
+        <v>15600</v>
+      </c>
+      <c r="H52" s="3">
         <v>13500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>13400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>10900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>10200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>9300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>9700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>9500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>7200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>7200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>6200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>6100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>6100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>6600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>5500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>4700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>4800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>3900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>3900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>4500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>4300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>3900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>3600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>6200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>5400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>4600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>4700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>2000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>2300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>1500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5171,121 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>468500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>473100</v>
+      </c>
+      <c r="F54" s="3">
         <v>470300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>474800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>482200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>483700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>481700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>503700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>509200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>508100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>481500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>449000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>385200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>336800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>312800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>312800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>317000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>327700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>363500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>355300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>369200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>371000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>378900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>379900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>384100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>369500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>341200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>313600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>298200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>292200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>275200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>260800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>261400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>263200</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5321,10 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,65 +5360,67 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>28100</v>
+      </c>
+      <c r="F57" s="3">
         <v>33500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>26300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>29400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>33500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>34200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>39000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>39200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>53300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>52800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>38500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>34600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>19000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>16400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>16400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>8300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>14500</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>8</v>
       </c>
@@ -5168,11 +5430,11 @@
       <c r="X57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>0</v>
+      <c r="Y57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA57" s="3">
         <v>0</v>
@@ -5201,379 +5463,403 @@
       <c r="AI57" s="3">
         <v>0</v>
       </c>
+      <c r="AJ57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>47100</v>
+        <v>49400</v>
       </c>
       <c r="E58" s="3">
-        <v>62300</v>
+        <v>54600</v>
       </c>
       <c r="F58" s="3">
-        <v>63400</v>
+        <v>51900</v>
       </c>
       <c r="G58" s="3">
-        <v>69000</v>
+        <v>67100</v>
       </c>
       <c r="H58" s="3">
-        <v>82200</v>
+        <v>68400</v>
       </c>
       <c r="I58" s="3">
+        <v>73700</v>
+      </c>
+      <c r="J58" s="3">
+        <v>87100</v>
+      </c>
+      <c r="K58" s="3">
         <v>106800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>117200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>114800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>113800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>104400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>59000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>32700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>21300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>21300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>35400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>42000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>74500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>65800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>82500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>88600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>100600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>107100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>111200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>110500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>90700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>77800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>67000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>67900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>56800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>49100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>50200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>43400</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>37900</v>
-      </c>
-      <c r="E59" s="3">
-        <v>40500</v>
-      </c>
-      <c r="F59" s="3">
-        <v>42700</v>
-      </c>
-      <c r="G59" s="3">
-        <v>39600</v>
-      </c>
-      <c r="H59" s="3">
-        <v>34900</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" s="3">
         <v>34800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>35500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>38100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>35200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>31900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>26900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>23500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>22000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>22000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>21000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>19500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>40700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>39900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>41800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>46400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>46000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>48100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>52500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>46700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>45300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>36400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>35400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>31400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>29100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>26200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>29200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>112300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>115800</v>
+      </c>
+      <c r="F60" s="3">
         <v>118500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>129200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>135500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>142100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>151300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>180600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>192000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>206200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>201800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>174800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>120500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>75200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>59600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>59600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>64700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>75900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>115200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>105700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>124400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>135000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>146600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>155200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>163600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>157100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>136000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>114200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>102400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>99200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>85900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>75300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>79300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>73500</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>20700</v>
+        <v>37200</v>
       </c>
       <c r="E61" s="3">
-        <v>20800</v>
+        <v>37300</v>
       </c>
       <c r="F61" s="3">
-        <v>20800</v>
+        <v>36400</v>
       </c>
       <c r="G61" s="3">
-        <v>20800</v>
+        <v>37700</v>
       </c>
       <c r="H61" s="3">
+        <v>39000</v>
+      </c>
+      <c r="I61" s="3">
+        <v>39100</v>
+      </c>
+      <c r="J61" s="3">
+        <v>37900</v>
+      </c>
+      <c r="K61" s="3">
         <v>20500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="L61" s="3">
         <v>20500</v>
       </c>
-      <c r="J61" s="3">
-        <v>20500</v>
-      </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>12600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>12800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>12900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>12900</v>
-      </c>
-      <c r="O61" s="3">
-        <v>13100</v>
-      </c>
-      <c r="P61" s="3">
-        <v>13100</v>
       </c>
       <c r="Q61" s="3">
         <v>13100</v>
       </c>
       <c r="R61" s="3">
-        <v>13000</v>
+        <v>13100</v>
       </c>
       <c r="S61" s="3">
         <v>13100</v>
       </c>
       <c r="T61" s="3">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="U61" s="3">
-        <v>12000</v>
+        <v>13100</v>
       </c>
       <c r="V61" s="3">
         <v>12000</v>
       </c>
       <c r="W61" s="3">
-        <v>12200</v>
+        <v>12000</v>
       </c>
       <c r="X61" s="3">
         <v>12000</v>
       </c>
       <c r="Y61" s="3">
-        <v>12000</v>
+        <v>12200</v>
       </c>
       <c r="Z61" s="3">
         <v>12000</v>
@@ -5605,109 +5891,121 @@
       <c r="AI61" s="3">
         <v>12000</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>12000</v>
+      </c>
+      <c r="AK61" s="3">
+        <v>12000</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>15700</v>
-      </c>
-      <c r="E62" s="3">
-        <v>16900</v>
-      </c>
-      <c r="F62" s="3">
-        <v>18100</v>
-      </c>
-      <c r="G62" s="3">
-        <v>18300</v>
+        <v>0</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H62" s="3">
-        <v>17400</v>
-      </c>
-      <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
         <v>17900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>16000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>17100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>17100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>18500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>20600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>23900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>22900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>22900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>22700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>22200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>19000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>21000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>15100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>8700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>7200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>7200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>8000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>8800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>7600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>7100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>12300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>12800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>11100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>9100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>8300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +6105,14 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6212,14 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6319,121 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>149500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>154000</v>
+      </c>
+      <c r="F66" s="3">
         <v>154900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>166800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>174500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>181200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>189200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>219000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>228400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>235900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>231700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>206200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>154100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>112200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>95700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>95700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>100400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>111200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>146200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>138700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>151500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>155900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>165800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>174400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>183700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>177900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>155600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>133300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>126700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>124000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>109000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>96500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>99700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>102500</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6469,10 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6572,14 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6679,14 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6786,14 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,89 +6893,95 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>264400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>264800</v>
+      </c>
+      <c r="F72" s="3">
         <v>255300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>255300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>255000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>249900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>241600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>235600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>232100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>223800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>201300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>193800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>181000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>171700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>165400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>165400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>165500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>165600</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X72" s="3">
+      <c r="X72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z72" s="3">
         <v>213100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>205600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>200500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>191500</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>8</v>
       </c>
@@ -6643,17 +6991,23 @@
       <c r="AF72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH72" s="3">
-        <v>0</v>
+      <c r="AG72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI72" s="3">
         <v>0</v>
       </c>
+      <c r="AJ72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +7107,14 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7214,14 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7321,121 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>319000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>319100</v>
+      </c>
+      <c r="F76" s="3">
         <v>315400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>308000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>307700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>302500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>292500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>284700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>280700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>272300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>249800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>242800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>231100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>224600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>217100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>217100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>216600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>216500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>217300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>216600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>217800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>215200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>213100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>205600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>200500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>191500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>185600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>180400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>171500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>168200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>166200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>164400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>161700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>160600</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7535,233 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45504</v>
+      </c>
+      <c r="F80" s="2">
         <v>45412</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45322</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45230</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45138</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45046</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44957</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44865</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44773</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44681</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44592</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44500</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44408</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44316</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44227</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44135</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44043</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43951</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43861</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43769</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43677</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43585</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43496</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43404</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43312</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43220</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43131</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43039</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42947</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42855</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42766</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42674</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F81" s="3">
         <v>6400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>5100</v>
       </c>
-      <c r="G81" s="3">
-        <v>8300</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
+        <v>7300</v>
+      </c>
+      <c r="J81" s="3">
         <v>6400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>3500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>8400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>8200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>16000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>9500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>14600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>13400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>6500</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
+        <v>0</v>
+      </c>
+      <c r="T81" s="3">
         <v>-200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-1100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>2000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>3200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>4300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>6600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>4900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>9800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>6800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>5000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>8400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>3000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>1400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>1300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>2200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,88 +7797,90 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>3900</v>
-      </c>
-      <c r="E83" s="3">
-        <v>3700</v>
-      </c>
-      <c r="F83" s="3">
-        <v>3700</v>
-      </c>
-      <c r="G83" s="3">
-        <v>3700</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K83" s="3">
         <v>3300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="L83" s="3">
         <v>3300</v>
       </c>
-      <c r="J83" s="3">
-        <v>3300</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>4100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>3500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>7000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>-10300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>3400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>3400</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>3500</v>
-      </c>
-      <c r="R83" s="3">
-        <v>3600</v>
       </c>
       <c r="S83" s="3">
         <v>3500</v>
       </c>
       <c r="T83" s="3">
-        <v>3400</v>
+        <v>3600</v>
       </c>
       <c r="U83" s="3">
         <v>3500</v>
       </c>
       <c r="V83" s="3">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="W83" s="3">
         <v>3500</v>
       </c>
       <c r="X83" s="3">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="Y83" s="3">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="Z83" s="3">
         <v>3400</v>
       </c>
       <c r="AA83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="AC83" s="3">
         <v>3300</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>3100</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>3000</v>
       </c>
       <c r="AD83" s="3">
         <v>3100</v>
@@ -7491,19 +7889,25 @@
         <v>3000</v>
       </c>
       <c r="AF83" s="3">
-        <v>2900</v>
+        <v>3100</v>
       </c>
       <c r="AG83" s="3">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="AH83" s="3">
         <v>2900</v>
       </c>
       <c r="AI83" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AJ83" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AK83" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +8007,14 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +8114,14 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8221,14 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8328,14 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8435,121 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>28400</v>
-      </c>
-      <c r="E89" s="3">
-        <v>9700</v>
-      </c>
-      <c r="F89" s="3">
-        <v>18100</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-46100</v>
-      </c>
-      <c r="H89" s="3">
-        <v>53200</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K89" s="3">
         <v>6700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>9400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>5100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-30200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-54700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-6300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>21200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>3600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>23600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>5000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>23000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>11100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>22600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>12900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>14800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>1400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-9500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-11800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>2500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>7800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,31 +8585,33 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -8246,8 +8688,14 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8795,14 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,31 +8902,37 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -8492,29 +8952,29 @@
       <c r="P94" s="3">
         <v>0</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>8</v>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T94" s="3">
         <v>4100</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y94" s="3">
         <v>0</v>
@@ -8549,8 +9009,14 @@
       <c r="AI94" s="3">
         <v>0</v>
       </c>
+      <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +9052,33 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8687,8 +9155,14 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9262,14 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9369,14 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,31 +9476,37 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -9091,31 +9583,37 @@
       <c r="AI100" s="3">
         <v>0</v>
       </c>
+      <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9192,31 +9690,37 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
@@ -9291,6 +9795,12 @@
         <v>0</v>
       </c>
       <c r="AI102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WEBC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WEBC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="92">
   <si>
     <t>WEBC</t>
   </si>
@@ -656,480 +656,493 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="2">
         <v>45596</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45504</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45412</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45322</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45230</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45138</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45046</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44957</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44865</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44773</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44592</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44500</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44408</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44316</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44227</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44135</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44043</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43951</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43861</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43769</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43677</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43585</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43496</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43404</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43312</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43220</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43131</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43039</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42947</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42855</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42766</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42674</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>129700</v>
+      </c>
+      <c r="E8" s="3">
         <v>141400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>151400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>153200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>146000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>157800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>156400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>168600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>173400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>188500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>172500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>190600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>173400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>167500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>145500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>127000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>94300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>99800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>89100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>104800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>112400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>122500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>130000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>145700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>135900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>137000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>147800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>127300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>111000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>114300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>106600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>98300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>91600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>88300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>84000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>119800</v>
+      </c>
+      <c r="E9" s="3">
         <v>127700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>133800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>133500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>133000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>136200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>131900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>145000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>158100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>162500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>151400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>157100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>144300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>133100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>116900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>108400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>87000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>92500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>86300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>94900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>100700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>108900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>118600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>126000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>117500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>112800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>123700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>108700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>98000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>100400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>96400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>89400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>84000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>80400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>77300</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E10" s="3">
         <v>13600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>17600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>19700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>13000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>21600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>24500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>23600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>15300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>26000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>21100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>33500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>29100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>34400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>28600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>18600</v>
-      </c>
-      <c r="S10" s="3">
-        <v>7300</v>
       </c>
       <c r="T10" s="3">
         <v>7300</v>
       </c>
       <c r="U10" s="3">
+        <v>7300</v>
+      </c>
+      <c r="V10" s="3">
         <v>2800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>9900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>11700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>13600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>11400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>19700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>18400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>24200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>24100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>18600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>13000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>13900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>10200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>8900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>7600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>7900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1167,8 +1180,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1274,8 +1288,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1381,8 +1398,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1407,8 +1427,8 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1416,8 +1436,8 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1437,15 +1457,15 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>400</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1461,8 +1481,8 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1488,8 +1508,11 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1497,13 +1520,13 @@
         <v>4700</v>
       </c>
       <c r="E15" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F15" s="3">
         <v>4300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3900</v>
-      </c>
-      <c r="G15" s="3">
-        <v>3700</v>
       </c>
       <c r="H15" s="3">
         <v>3700</v>
@@ -1512,11 +1535,11 @@
         <v>3700</v>
       </c>
       <c r="J15" s="3">
+        <v>3700</v>
+      </c>
+      <c r="K15" s="3">
         <v>3300</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1595,8 +1618,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,222 +1657,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>131500</v>
+      </c>
+      <c r="E17" s="3">
         <v>140300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>147100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>146100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>144500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>149900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>146000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>157200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>168700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>176100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>161400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>169500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>160200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>148100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>128500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>118500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>94100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>99600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>91000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>104200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>109100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>117700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>124900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>135700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>127800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>123100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>137500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>120100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>106400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>108500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>103600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>95800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>89800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>86800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>83300</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E18" s="3">
         <v>1100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>8000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>10500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>11400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>12400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>21100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>13200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>19400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>17000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>8500</v>
-      </c>
-      <c r="S18" s="3">
-        <v>200</v>
       </c>
       <c r="T18" s="3">
         <v>200</v>
       </c>
       <c r="U18" s="3">
+        <v>200</v>
+      </c>
+      <c r="V18" s="3">
         <v>-1900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>5100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>10000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>8100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>13900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>10300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>7200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>4600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>5800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1884,28 +1917,29 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1950,156 +1984,162 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-300</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>200</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
       <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
         <v>200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E21" s="3">
         <v>5800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>8600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>11000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>11700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>14200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>14700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>15700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>15200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>24500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>20200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>9100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>20500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>11900</v>
-      </c>
-      <c r="S21" s="3">
-        <v>3800</v>
       </c>
       <c r="T21" s="3">
         <v>3800</v>
       </c>
       <c r="U21" s="3">
+        <v>3800</v>
+      </c>
+      <c r="V21" s="3">
         <v>1700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>6900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>8300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>8400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>13300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>11200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>17300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>13700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>10500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>8000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>9100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>6100</v>
-      </c>
-      <c r="AH21" s="3">
-        <v>5600</v>
       </c>
       <c r="AI21" s="3">
         <v>5600</v>
       </c>
       <c r="AJ21" s="3">
+        <v>5600</v>
+      </c>
+      <c r="AK21" s="3">
         <v>4900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2107,320 +2147,329 @@
         <v>1200</v>
       </c>
       <c r="E22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F22" s="3">
         <v>1000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1100</v>
-      </c>
-      <c r="H22" s="3">
-        <v>1300</v>
       </c>
       <c r="I22" s="3">
         <v>1300</v>
       </c>
       <c r="J22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K22" s="3">
         <v>1600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>400</v>
-      </c>
-      <c r="R22" s="3">
-        <v>300</v>
       </c>
       <c r="S22" s="3">
         <v>300</v>
       </c>
       <c r="T22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="U22" s="3">
         <v>400</v>
       </c>
       <c r="V22" s="3">
+        <v>400</v>
+      </c>
+      <c r="W22" s="3">
         <v>700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1200</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>1300</v>
       </c>
       <c r="AB22" s="3">
         <v>1300</v>
       </c>
       <c r="AC22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AD22" s="3">
         <v>1100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>900</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>800</v>
       </c>
       <c r="AF22" s="3">
         <v>800</v>
       </c>
       <c r="AG22" s="3">
+        <v>800</v>
+      </c>
+      <c r="AH22" s="3">
         <v>600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>600</v>
-      </c>
-      <c r="AJ22" s="3">
-        <v>700</v>
       </c>
       <c r="AK22" s="3">
         <v>700</v>
       </c>
+      <c r="AL22" s="3">
+        <v>700</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>6700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>9200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>10900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>9900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>20300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>12600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>18800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>16700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>8200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>8700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>6500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>12500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>9200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>6500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>5200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-900</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1700</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>-1200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-4200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2526,222 +2575,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>8400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>8200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>16000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>9500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>14600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>13400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>6500</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
       <c r="T26" s="3">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
         <v>-200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>6600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>9800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>6800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>5000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>8400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>8400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>8200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>16000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>9500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>14600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>13400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>6500</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3">
         <v>-200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>6600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>9800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>6800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>5000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>8400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2847,8 +2905,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2954,8 +3015,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3061,8 +3125,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3168,28 +3235,31 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -3234,156 +3304,162 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>300</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-200</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
       <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>8400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>8200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>16000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>9500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>14600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>13400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>6500</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3">
         <v>-200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>6600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>4900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>9800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>6800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>5000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>8400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3489,227 +3565,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>8400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>8200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>16000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>9500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>14600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>13400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>6500</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
         <v>-200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>6600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>4900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>9800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>6800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>5000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>8400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E38" s="2">
         <v>45596</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45504</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45412</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45322</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45230</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45138</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45046</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44957</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44865</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44773</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44592</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44500</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44408</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44316</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44227</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44135</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44043</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43951</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43861</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43769</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43677</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43585</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43496</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43404</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43312</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43220</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43131</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43039</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42947</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42855</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42766</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42674</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3747,8 +3832,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3786,145 +3872,149 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E41" s="3">
         <v>2500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>12800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7100</v>
-      </c>
-      <c r="R41" s="3">
-        <v>5400</v>
       </c>
       <c r="S41" s="3">
         <v>5400</v>
       </c>
       <c r="T41" s="3">
+        <v>5400</v>
+      </c>
+      <c r="U41" s="3">
         <v>6200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>11300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>7100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>7200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>8100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>8000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>8400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E42" s="3">
         <v>16100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>15900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>15400</v>
-      </c>
-      <c r="G42" s="3">
-        <v>14800</v>
       </c>
       <c r="H42" s="3">
         <v>14800</v>
       </c>
       <c r="I42" s="3">
+        <v>14800</v>
+      </c>
+      <c r="J42" s="3">
         <v>15900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>14600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>10600</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>8</v>
       </c>
@@ -3940,8 +4030,8 @@
       <c r="Q42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -4000,436 +4090,451 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>61300</v>
+      </c>
+      <c r="E43" s="3">
         <v>58700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>70200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>70100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>73400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>73600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>68500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>78200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>87000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>87400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>83700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>79500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>83700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>75200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>59900</v>
-      </c>
-      <c r="R43" s="3">
-        <v>45000</v>
       </c>
       <c r="S43" s="3">
         <v>45000</v>
       </c>
       <c r="T43" s="3">
+        <v>45000</v>
+      </c>
+      <c r="U43" s="3">
         <v>48900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>41700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>47300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>54200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>55600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>59400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>67200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>64400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>64700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>76500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>68800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>55500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>54700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>53000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>49500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>43000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>39700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>39900</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>178800</v>
+      </c>
+      <c r="E44" s="3">
         <v>174700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>169500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>174900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>181300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>193400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>208000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>208700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>219000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>234700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>244300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>232600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>203000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>149800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>121100</v>
-      </c>
-      <c r="R44" s="3">
-        <v>114900</v>
       </c>
       <c r="S44" s="3">
         <v>114900</v>
       </c>
       <c r="T44" s="3">
+        <v>114900</v>
+      </c>
+      <c r="U44" s="3">
         <v>112500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>135800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>160200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>156300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>168800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>176400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>185800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>197900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>198600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>170900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>153700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>144900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>130700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>124500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>115200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>112600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>117000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>113400</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
         <v>0</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>8</v>
+      <c r="E45" s="3">
+        <v>0</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3">
+        <v>0</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J45" s="3">
-        <v>0</v>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K45" s="3">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3">
         <v>15000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>11800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6700</v>
-      </c>
-      <c r="R45" s="3">
-        <v>2400</v>
       </c>
       <c r="S45" s="3">
         <v>2400</v>
       </c>
       <c r="T45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="U45" s="3">
         <v>7400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>6700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>11800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>11600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>6700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>5300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>7200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>5700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>5900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>5500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>262300</v>
+      </c>
+      <c r="E46" s="3">
         <v>261200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>266400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>269600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>277300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>292900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>301100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>309900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>335300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>348800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>352600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>331100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>304000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>240600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>194800</v>
-      </c>
-      <c r="R46" s="3">
-        <v>167700</v>
       </c>
       <c r="S46" s="3">
         <v>167700</v>
       </c>
       <c r="T46" s="3">
+        <v>167700</v>
+      </c>
+      <c r="U46" s="3">
         <v>175100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>187600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>225500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>215800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>242500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>254600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>266400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>270900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>274800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>261700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>232500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>210100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>197600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>190200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>176300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>164800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>166700</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>169300</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4454,8 +4559,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4535,115 +4640,121 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>192000</v>
+      </c>
+      <c r="E48" s="3">
         <v>191600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>191100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>184000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>182000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>175800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>169100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>160800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>158100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>151000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>145900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>140800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>137800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>137400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>135700</v>
-      </c>
-      <c r="R48" s="3">
-        <v>139000</v>
       </c>
       <c r="S48" s="3">
         <v>139000</v>
       </c>
       <c r="T48" s="3">
+        <v>139000</v>
+      </c>
+      <c r="U48" s="3">
         <v>135400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>134600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>133400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>134700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>122800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>112500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>107900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>104700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>105500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>104200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>102500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>98100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>96100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>97200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>96900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>93700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>93200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>92600</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4749,8 +4860,11 @@
       <c r="AK49" s="3">
         <v>0</v>
       </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4856,8 +4970,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4963,115 +5080,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E52" s="3">
         <v>15700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>15600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>16700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>15600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>13500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9500</v>
-      </c>
-      <c r="O52" s="3">
-        <v>7200</v>
       </c>
       <c r="P52" s="3">
         <v>7200</v>
       </c>
       <c r="Q52" s="3">
+        <v>7200</v>
+      </c>
+      <c r="R52" s="3">
         <v>6200</v>
-      </c>
-      <c r="R52" s="3">
-        <v>6100</v>
       </c>
       <c r="S52" s="3">
         <v>6100</v>
       </c>
       <c r="T52" s="3">
+        <v>6100</v>
+      </c>
+      <c r="U52" s="3">
         <v>6600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4800</v>
-      </c>
-      <c r="X52" s="3">
-        <v>3900</v>
       </c>
       <c r="Y52" s="3">
         <v>3900</v>
       </c>
       <c r="Z52" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AA52" s="3">
         <v>4500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>4600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>4700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5177,115 +5300,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>469400</v>
+      </c>
+      <c r="E54" s="3">
         <v>468500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>473100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>470300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>474800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>482200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>483700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>481700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>503700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>509200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>508100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>481500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>449000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>385200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>336800</v>
-      </c>
-      <c r="R54" s="3">
-        <v>312800</v>
       </c>
       <c r="S54" s="3">
         <v>312800</v>
       </c>
       <c r="T54" s="3">
+        <v>312800</v>
+      </c>
+      <c r="U54" s="3">
         <v>317000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>327700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>363500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>355300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>369200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>371000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>378900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>379900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>384100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>369500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>341200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>313600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>298200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>292200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>275200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>260800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>261400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>263200</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5323,8 +5452,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5362,68 +5492,69 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E57" s="3">
         <v>30200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>28100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>33500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>26300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>29400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>33500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>34200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>39000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>39200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>53300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>52800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>38500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>34600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>19000</v>
-      </c>
-      <c r="R57" s="3">
-        <v>16400</v>
       </c>
       <c r="S57" s="3">
         <v>16400</v>
       </c>
       <c r="T57" s="3">
+        <v>16400</v>
+      </c>
+      <c r="U57" s="3">
         <v>8300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>14500</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>8</v>
       </c>
@@ -5436,8 +5567,8 @@
       <c r="Z57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA57" s="3">
-        <v>0</v>
+      <c r="AA57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB57" s="3">
         <v>0</v>
@@ -5469,115 +5600,121 @@
       <c r="AK57" s="3">
         <v>0</v>
       </c>
+      <c r="AL57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>83200</v>
+      </c>
+      <c r="E58" s="3">
         <v>49400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>54600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>51900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>67100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>68400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>73700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>87100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>106800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>117200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>114800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>113800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>104400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>59000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>32700</v>
-      </c>
-      <c r="R58" s="3">
-        <v>21300</v>
       </c>
       <c r="S58" s="3">
         <v>21300</v>
       </c>
       <c r="T58" s="3">
+        <v>21300</v>
+      </c>
+      <c r="U58" s="3">
         <v>35400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>42000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>74500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>65800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>82500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>88600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>100600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>107100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>111200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>110500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>90700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>77800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>67000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>67900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>56800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>49100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>50200</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>43400</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5602,240 +5739,246 @@
       <c r="J59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L59" s="3">
         <v>34800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>35500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>38100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>35200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>31900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>26900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>23500</v>
-      </c>
-      <c r="R59" s="3">
-        <v>22000</v>
       </c>
       <c r="S59" s="3">
         <v>22000</v>
       </c>
       <c r="T59" s="3">
+        <v>22000</v>
+      </c>
+      <c r="U59" s="3">
         <v>21000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>19500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>40700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>39900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>41800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>46400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>46000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>48100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>52500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>46700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>45300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>36400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>35400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>31400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>29100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>26200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>29200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>144400</v>
+      </c>
+      <c r="E60" s="3">
         <v>112300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>115800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>118500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>129200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>135500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>142100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>151300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>180600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>192000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>206200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>201800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>174800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>120500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>75200</v>
-      </c>
-      <c r="R60" s="3">
-        <v>59600</v>
       </c>
       <c r="S60" s="3">
         <v>59600</v>
       </c>
       <c r="T60" s="3">
+        <v>59600</v>
+      </c>
+      <c r="U60" s="3">
         <v>64700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>75900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>115200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>105700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>124400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>135000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>146600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>155200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>163600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>157100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>136000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>114200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>102400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>99200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>85900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>75300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>79300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>73500</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>36500</v>
+      </c>
+      <c r="E61" s="3">
         <v>37200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>37300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>36400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>37700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>39000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>39100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>37900</v>
-      </c>
-      <c r="K61" s="3">
-        <v>20500</v>
       </c>
       <c r="L61" s="3">
         <v>20500</v>
       </c>
       <c r="M61" s="3">
+        <v>20500</v>
+      </c>
+      <c r="N61" s="3">
         <v>12600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>12800</v>
-      </c>
-      <c r="O61" s="3">
-        <v>12900</v>
       </c>
       <c r="P61" s="3">
         <v>12900</v>
       </c>
       <c r="Q61" s="3">
-        <v>13100</v>
+        <v>12900</v>
       </c>
       <c r="R61" s="3">
         <v>13100</v>
@@ -5844,13 +5987,13 @@
         <v>13100</v>
       </c>
       <c r="T61" s="3">
+        <v>13100</v>
+      </c>
+      <c r="U61" s="3">
         <v>13000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>13100</v>
-      </c>
-      <c r="V61" s="3">
-        <v>12000</v>
       </c>
       <c r="W61" s="3">
         <v>12000</v>
@@ -5859,10 +6002,10 @@
         <v>12000</v>
       </c>
       <c r="Y61" s="3">
+        <v>12000</v>
+      </c>
+      <c r="Z61" s="3">
         <v>12200</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>12000</v>
       </c>
       <c r="AA61" s="3">
         <v>12000</v>
@@ -5897,16 +6040,19 @@
       <c r="AK61" s="3">
         <v>12000</v>
       </c>
+      <c r="AL61" s="3">
+        <v>12000</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>8</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>8</v>
@@ -5914,98 +6060,101 @@
       <c r="G62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3">
         <v>17900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16000</v>
-      </c>
-      <c r="M62" s="3">
-        <v>17100</v>
       </c>
       <c r="N62" s="3">
         <v>17100</v>
       </c>
       <c r="O62" s="3">
+        <v>17100</v>
+      </c>
+      <c r="P62" s="3">
         <v>18500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>20600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>23900</v>
-      </c>
-      <c r="R62" s="3">
-        <v>22900</v>
       </c>
       <c r="S62" s="3">
         <v>22900</v>
       </c>
       <c r="T62" s="3">
+        <v>22900</v>
+      </c>
+      <c r="U62" s="3">
         <v>22700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>22200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>19000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>21000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>15100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8700</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>7200</v>
       </c>
       <c r="AA62" s="3">
         <v>7200</v>
       </c>
       <c r="AB62" s="3">
+        <v>7200</v>
+      </c>
+      <c r="AC62" s="3">
         <v>8000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>7600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>7100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>12300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>12800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>11100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>9100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>8300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6111,8 +6260,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6218,8 +6370,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6325,115 +6480,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>180900</v>
+      </c>
+      <c r="E66" s="3">
         <v>149500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>154000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>154900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>166800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>174500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>181200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>189200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>219000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>228400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>235900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>231700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>206200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>154100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>112200</v>
-      </c>
-      <c r="R66" s="3">
-        <v>95700</v>
       </c>
       <c r="S66" s="3">
         <v>95700</v>
       </c>
       <c r="T66" s="3">
+        <v>95700</v>
+      </c>
+      <c r="U66" s="3">
         <v>100400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>111200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>146200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>138700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>151500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>155900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>165800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>174400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>183700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>177900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>155600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>133300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>126700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>124000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>109000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>96500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>99700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>102500</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6471,8 +6632,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6578,8 +6740,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6685,8 +6850,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6792,8 +6960,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6899,68 +7070,71 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>242500</v>
+      </c>
+      <c r="E72" s="3">
         <v>264400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>264800</v>
-      </c>
-      <c r="F72" s="3">
-        <v>255300</v>
       </c>
       <c r="G72" s="3">
         <v>255300</v>
       </c>
       <c r="H72" s="3">
+        <v>255300</v>
+      </c>
+      <c r="I72" s="3">
         <v>255000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>249900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>241600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>235600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>232100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>223800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>201300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>193800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>181000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>171700</v>
-      </c>
-      <c r="R72" s="3">
-        <v>165400</v>
       </c>
       <c r="S72" s="3">
         <v>165400</v>
       </c>
       <c r="T72" s="3">
+        <v>165400</v>
+      </c>
+      <c r="U72" s="3">
         <v>165500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>165600</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>8</v>
       </c>
@@ -6970,21 +7144,21 @@
       <c r="Y72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="Z72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA72" s="3">
         <v>213100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>205600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>200500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>191500</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>8</v>
       </c>
@@ -6997,8 +7171,8 @@
       <c r="AH72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI72" s="3">
-        <v>0</v>
+      <c r="AI72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ72" s="3">
         <v>0</v>
@@ -7006,8 +7180,11 @@
       <c r="AK72" s="3">
         <v>0</v>
       </c>
+      <c r="AL72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7113,8 +7290,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7220,8 +7400,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7327,115 +7510,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>288600</v>
+      </c>
+      <c r="E76" s="3">
         <v>319000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>319100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>315400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>308000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>307700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>302500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>292500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>284700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>280700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>272300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>249800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>242800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>231100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>224600</v>
-      </c>
-      <c r="R76" s="3">
-        <v>217100</v>
       </c>
       <c r="S76" s="3">
         <v>217100</v>
       </c>
       <c r="T76" s="3">
+        <v>217100</v>
+      </c>
+      <c r="U76" s="3">
         <v>216600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>216500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>217300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>216600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>217800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>215200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>213100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>205600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>200500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>191500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>185600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>180400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>171500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>168200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>166200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>164400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>161700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>160600</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7541,227 +7730,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E80" s="2">
         <v>45596</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45504</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45412</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45322</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45230</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45138</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45046</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44957</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44865</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44773</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44592</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44500</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44408</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44316</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44227</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44135</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44043</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43951</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43861</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43769</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43677</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43585</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43496</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43404</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43312</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43220</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43131</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43039</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42947</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42855</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42766</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42674</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>8400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>8200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>16000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>9500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>14600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>13400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>6500</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3">
         <v>-200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>6600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>4900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>9800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>6800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>5000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>8400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7799,8 +7997,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7825,44 +8024,44 @@
       <c r="J83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K83" s="3">
-        <v>3300</v>
+      <c r="K83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L83" s="3">
         <v>3300</v>
       </c>
       <c r="M83" s="3">
+        <v>3300</v>
+      </c>
+      <c r="N83" s="3">
         <v>4100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>-10300</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>3400</v>
       </c>
       <c r="R83" s="3">
         <v>3400</v>
       </c>
       <c r="S83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="T83" s="3">
         <v>3500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3400</v>
-      </c>
-      <c r="W83" s="3">
-        <v>3500</v>
       </c>
       <c r="X83" s="3">
         <v>3500</v>
@@ -7871,7 +8070,7 @@
         <v>3500</v>
       </c>
       <c r="Z83" s="3">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="AA83" s="3">
         <v>3400</v>
@@ -7880,22 +8079,22 @@
         <v>3400</v>
       </c>
       <c r="AC83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="AD83" s="3">
         <v>3300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>3100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>3000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>3100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>3000</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>2900</v>
       </c>
       <c r="AI83" s="3">
         <v>2900</v>
@@ -7904,10 +8103,13 @@
         <v>2900</v>
       </c>
       <c r="AK83" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AL83" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8013,8 +8215,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8120,8 +8325,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8227,8 +8435,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8334,8 +8545,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8441,8 +8655,11 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8467,89 +8684,92 @@
       <c r="J89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L89" s="3">
         <v>6700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>9400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-30200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-54700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-6300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>21200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>23600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>5000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>23000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>11100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>22600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>12900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>14800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-9500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-2500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>7800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8587,8 +8807,9 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8613,8 +8834,8 @@
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -8694,8 +8915,11 @@
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8801,8 +9025,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8908,8 +9135,11 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8934,8 +9164,8 @@
       <c r="J94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -8958,15 +9188,15 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T94" s="3">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U94" s="3">
         <v>4100</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>8</v>
       </c>
@@ -8976,8 +9206,8 @@
       <c r="X94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
@@ -9015,8 +9245,11 @@
       <c r="AK94" s="3">
         <v>0</v>
       </c>
+      <c r="AL94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9054,8 +9287,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9080,8 +9314,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -9161,8 +9395,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9268,8 +9505,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9375,8 +9615,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9482,8 +9725,11 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9508,8 +9754,8 @@
       <c r="J100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -9589,8 +9835,11 @@
       <c r="AK100" s="3">
         <v>0</v>
       </c>
+      <c r="AL100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9615,8 +9864,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9696,8 +9945,11 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9722,8 +9974,8 @@
       <c r="J102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
+      <c r="K102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
@@ -9801,6 +10053,9 @@
         <v>0</v>
       </c>
       <c r="AK102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WEBC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WEBC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="92">
   <si>
     <t>WEBC</t>
   </si>
@@ -656,493 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E7" s="2">
         <v>45688</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45596</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45504</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45412</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45322</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45230</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45138</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45046</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44957</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44865</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44773</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44681</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44592</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44500</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44408</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44316</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44227</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44135</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44043</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43951</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43861</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43769</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43677</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43585</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43496</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43404</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43312</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43220</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43131</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43039</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42947</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42766</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42674</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>129700</v>
-      </c>
-      <c r="E8" s="3">
-        <v>141400</v>
-      </c>
-      <c r="F8" s="3">
-        <v>151400</v>
-      </c>
-      <c r="G8" s="3">
-        <v>153200</v>
-      </c>
-      <c r="H8" s="3">
-        <v>146000</v>
-      </c>
-      <c r="I8" s="3">
-        <v>157800</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="3">
         <v>156400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>168600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>173400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>188500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>172500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>190600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>173400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>167500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>145500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>127000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>94300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>99800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>89100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>104800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>112400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>122500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>130000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>145700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>135900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>137000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>147800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>127300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>111000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>114300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>106600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>98300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>91600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>88300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>84000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>119800</v>
-      </c>
-      <c r="E9" s="3">
-        <v>127700</v>
-      </c>
-      <c r="F9" s="3">
-        <v>133800</v>
-      </c>
-      <c r="G9" s="3">
-        <v>133500</v>
-      </c>
-      <c r="H9" s="3">
-        <v>133000</v>
-      </c>
-      <c r="I9" s="3">
-        <v>136200</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
         <v>131900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>145000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>158100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>162500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>151400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>157100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>144300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>133100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>116900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>108400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>87000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>92500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>86300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>94900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>100700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>108900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>118600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>126000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>117500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>112800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>123700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>108700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>98000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>100400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>96400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>89400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>84000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>80400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>77300</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>9900</v>
-      </c>
-      <c r="E10" s="3">
-        <v>13600</v>
-      </c>
-      <c r="F10" s="3">
-        <v>17600</v>
-      </c>
-      <c r="G10" s="3">
-        <v>19700</v>
-      </c>
-      <c r="H10" s="3">
-        <v>13000</v>
-      </c>
-      <c r="I10" s="3">
-        <v>21600</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="3">
         <v>24500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>23600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>15300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>26000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>21100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>33500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>29100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>34400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>28600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>18600</v>
-      </c>
-      <c r="T10" s="3">
-        <v>7300</v>
       </c>
       <c r="U10" s="3">
         <v>7300</v>
       </c>
       <c r="V10" s="3">
+        <v>7300</v>
+      </c>
+      <c r="W10" s="3">
         <v>2800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>9900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>11700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>13600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>11400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>19700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>18400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>24200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>24100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>18600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>13000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>13900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>10200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>8900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>7600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>7900</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1181,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1291,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1401,8 +1417,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1430,8 +1449,8 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1439,8 +1458,8 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
@@ -1460,15 +1479,15 @@
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3">
         <v>500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>400</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1484,8 +1503,8 @@
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
@@ -1511,38 +1530,41 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>4700</v>
-      </c>
-      <c r="E15" s="3">
-        <v>4700</v>
-      </c>
-      <c r="F15" s="3">
-        <v>4300</v>
-      </c>
-      <c r="G15" s="3">
-        <v>3900</v>
-      </c>
-      <c r="H15" s="3">
+      <c r="D15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="3">
         <v>3700</v>
       </c>
-      <c r="I15" s="3">
-        <v>3700</v>
-      </c>
-      <c r="J15" s="3">
-        <v>3700</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3300</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1621,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1658,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>131500</v>
-      </c>
-      <c r="E17" s="3">
-        <v>140300</v>
-      </c>
-      <c r="F17" s="3">
-        <v>147100</v>
-      </c>
-      <c r="G17" s="3">
-        <v>146100</v>
-      </c>
-      <c r="H17" s="3">
-        <v>144500</v>
-      </c>
-      <c r="I17" s="3">
-        <v>149900</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="3">
         <v>146000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>157200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>168700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>176100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>161400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>169500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>160200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>148100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>128500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>118500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>94100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>99600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>91000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>104200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>109100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>117700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>124900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>135700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>127800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>123100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>137500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>120100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>106400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>108500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>103600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>95800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>89800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>86800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>83300</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="E18" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F18" s="3">
-        <v>4300</v>
-      </c>
-      <c r="G18" s="3">
-        <v>7100</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1500</v>
-      </c>
-      <c r="I18" s="3">
-        <v>8000</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="3">
         <v>10500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>11400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>12400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>11100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>21100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>19400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>17000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>8500</v>
-      </c>
-      <c r="T18" s="3">
-        <v>200</v>
       </c>
       <c r="U18" s="3">
         <v>200</v>
       </c>
       <c r="V18" s="3">
+        <v>200</v>
+      </c>
+      <c r="W18" s="3">
         <v>-1900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>5100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>10000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>8100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>13900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>10300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>7200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>4600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>5800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1918,13 +1950,14 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>8</v>
@@ -1932,17 +1965,17 @@
       <c r="F20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1987,489 +2020,504 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-300</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>200</v>
       </c>
-      <c r="AH20" s="3">
-        <v>0</v>
-      </c>
       <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>2900</v>
-      </c>
-      <c r="E21" s="3">
-        <v>5800</v>
-      </c>
-      <c r="F21" s="3">
-        <v>8600</v>
-      </c>
-      <c r="G21" s="3">
-        <v>11000</v>
-      </c>
-      <c r="H21" s="3">
-        <v>5300</v>
-      </c>
-      <c r="I21" s="3">
-        <v>11700</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="3">
         <v>14200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>14700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>15700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>15200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>24500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>20200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>9100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>20500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>11900</v>
-      </c>
-      <c r="T21" s="3">
-        <v>3800</v>
       </c>
       <c r="U21" s="3">
         <v>3800</v>
       </c>
       <c r="V21" s="3">
+        <v>3800</v>
+      </c>
+      <c r="W21" s="3">
         <v>1700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>6900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>8300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>8400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>13300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>11200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>17300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>13700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>10500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>8000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>9100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>6100</v>
-      </c>
-      <c r="AI21" s="3">
-        <v>5600</v>
       </c>
       <c r="AJ21" s="3">
         <v>5600</v>
       </c>
       <c r="AK21" s="3">
+        <v>5600</v>
+      </c>
+      <c r="AL21" s="3">
         <v>4900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L22" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M22" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N22" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O22" s="3">
         <v>1200</v>
       </c>
-      <c r="E22" s="3">
-        <v>1200</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="P22" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q22" s="3">
         <v>700</v>
       </c>
-      <c r="H22" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I22" s="3">
-        <v>1300</v>
-      </c>
-      <c r="J22" s="3">
-        <v>1300</v>
-      </c>
-      <c r="K22" s="3">
-        <v>1600</v>
-      </c>
-      <c r="L22" s="3">
-        <v>1700</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1500</v>
-      </c>
-      <c r="N22" s="3">
-        <v>1200</v>
-      </c>
-      <c r="O22" s="3">
-        <v>800</v>
-      </c>
-      <c r="P22" s="3">
-        <v>700</v>
-      </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>400</v>
-      </c>
-      <c r="S22" s="3">
-        <v>300</v>
       </c>
       <c r="T22" s="3">
         <v>300</v>
       </c>
       <c r="U22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="V22" s="3">
         <v>400</v>
       </c>
       <c r="W22" s="3">
+        <v>400</v>
+      </c>
+      <c r="X22" s="3">
         <v>700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1200</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>1300</v>
       </c>
       <c r="AC22" s="3">
         <v>1300</v>
       </c>
       <c r="AD22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AE22" s="3">
         <v>1100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>900</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>800</v>
       </c>
       <c r="AG22" s="3">
         <v>800</v>
       </c>
       <c r="AH22" s="3">
+        <v>800</v>
+      </c>
+      <c r="AI22" s="3">
         <v>600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>600</v>
-      </c>
-      <c r="AK22" s="3">
-        <v>700</v>
       </c>
       <c r="AL22" s="3">
         <v>700</v>
       </c>
+      <c r="AM22" s="3">
+        <v>700</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="E23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="3">
+        <v>9200</v>
+      </c>
+      <c r="L23" s="3">
+        <v>9800</v>
+      </c>
+      <c r="M23" s="3">
+        <v>2900</v>
+      </c>
+      <c r="N23" s="3">
+        <v>10900</v>
+      </c>
+      <c r="O23" s="3">
+        <v>9900</v>
+      </c>
+      <c r="P23" s="3">
+        <v>20300</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>12600</v>
+      </c>
+      <c r="R23" s="3">
+        <v>18800</v>
+      </c>
+      <c r="S23" s="3">
+        <v>16700</v>
+      </c>
+      <c r="T23" s="3">
+        <v>8200</v>
+      </c>
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
-      <c r="F23" s="3">
-        <v>3400</v>
-      </c>
-      <c r="G23" s="3">
-        <v>6400</v>
-      </c>
-      <c r="H23" s="3">
-        <v>500</v>
-      </c>
-      <c r="I23" s="3">
-        <v>6700</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="V23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="X23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>2500</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AB23" s="3">
+        <v>8700</v>
+      </c>
+      <c r="AC23" s="3">
+        <v>6500</v>
+      </c>
+      <c r="AD23" s="3">
+        <v>12500</v>
+      </c>
+      <c r="AE23" s="3">
         <v>9200</v>
       </c>
-      <c r="K23" s="3">
-        <v>9800</v>
-      </c>
-      <c r="L23" s="3">
-        <v>2900</v>
-      </c>
-      <c r="M23" s="3">
-        <v>10900</v>
-      </c>
-      <c r="N23" s="3">
-        <v>9900</v>
-      </c>
-      <c r="O23" s="3">
-        <v>20300</v>
-      </c>
-      <c r="P23" s="3">
-        <v>12600</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>18800</v>
-      </c>
-      <c r="R23" s="3">
-        <v>16700</v>
-      </c>
-      <c r="S23" s="3">
-        <v>8200</v>
-      </c>
-      <c r="T23" s="3">
-        <v>-100</v>
-      </c>
-      <c r="U23" s="3">
+      <c r="AF23" s="3">
+        <v>6500</v>
+      </c>
+      <c r="AG23" s="3">
+        <v>4200</v>
+      </c>
+      <c r="AH23" s="3">
+        <v>5200</v>
+      </c>
+      <c r="AI23" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AJ23" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AK23" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AL23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AM23" s="3">
         <v>-200</v>
       </c>
-      <c r="V23" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-100</v>
-      </c>
-      <c r="X23" s="3">
-        <v>2500</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>3800</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>4000</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>8700</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>6500</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>12500</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>9200</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>6500</v>
-      </c>
-      <c r="AF23" s="3">
-        <v>4200</v>
-      </c>
-      <c r="AG23" s="3">
-        <v>5200</v>
-      </c>
-      <c r="AH23" s="3">
-        <v>2400</v>
-      </c>
-      <c r="AI23" s="3">
-        <v>2200</v>
-      </c>
-      <c r="AJ23" s="3">
-        <v>2000</v>
-      </c>
-      <c r="AK23" s="3">
-        <v>1300</v>
-      </c>
-      <c r="AL23" s="3">
-        <v>-200</v>
-      </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>100</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L24" s="3">
+        <v>3500</v>
+      </c>
+      <c r="M24" s="3">
+        <v>-600</v>
+      </c>
+      <c r="N24" s="3">
+        <v>2500</v>
+      </c>
+      <c r="O24" s="3">
+        <v>1700</v>
+      </c>
+      <c r="P24" s="3">
+        <v>4300</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R24" s="3">
+        <v>4200</v>
+      </c>
+      <c r="S24" s="3">
+        <v>3300</v>
+      </c>
+      <c r="T24" s="3">
+        <v>1700</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="X24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>700</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AC24" s="3">
         <v>1600</v>
       </c>
-      <c r="J24" s="3">
-        <v>1800</v>
-      </c>
-      <c r="K24" s="3">
-        <v>3500</v>
-      </c>
-      <c r="L24" s="3">
-        <v>-600</v>
-      </c>
-      <c r="M24" s="3">
-        <v>2500</v>
-      </c>
-      <c r="N24" s="3">
-        <v>1700</v>
-      </c>
-      <c r="O24" s="3">
-        <v>4300</v>
-      </c>
-      <c r="P24" s="3">
-        <v>3000</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>4200</v>
-      </c>
-      <c r="R24" s="3">
-        <v>3300</v>
-      </c>
-      <c r="S24" s="3">
-        <v>1700</v>
-      </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
-      <c r="V24" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="W24" s="3">
-        <v>-300</v>
-      </c>
-      <c r="X24" s="3">
-        <v>500</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>700</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>2100</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>1600</v>
-      </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-4200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2578,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="3">
+        <v>7300</v>
+      </c>
+      <c r="L26" s="3">
+        <v>6400</v>
+      </c>
+      <c r="M26" s="3">
+        <v>3500</v>
+      </c>
+      <c r="N26" s="3">
+        <v>8400</v>
+      </c>
+      <c r="O26" s="3">
+        <v>8200</v>
+      </c>
+      <c r="P26" s="3">
+        <v>16000</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>9500</v>
+      </c>
+      <c r="R26" s="3">
+        <v>14600</v>
+      </c>
+      <c r="S26" s="3">
+        <v>13400</v>
+      </c>
+      <c r="T26" s="3">
+        <v>6500</v>
+      </c>
+      <c r="U26" s="3">
+        <v>0</v>
+      </c>
+      <c r="V26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="X26" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AA26" s="3">
         <v>4300</v>
       </c>
-      <c r="G26" s="3">
-        <v>6400</v>
-      </c>
-      <c r="H26" s="3">
-        <v>300</v>
-      </c>
-      <c r="I26" s="3">
-        <v>5100</v>
-      </c>
-      <c r="J26" s="3">
-        <v>7300</v>
-      </c>
-      <c r="K26" s="3">
-        <v>6400</v>
-      </c>
-      <c r="L26" s="3">
-        <v>3500</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="AB26" s="3">
+        <v>6600</v>
+      </c>
+      <c r="AC26" s="3">
+        <v>4900</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>9800</v>
+      </c>
+      <c r="AE26" s="3">
+        <v>6800</v>
+      </c>
+      <c r="AF26" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AG26" s="3">
         <v>8400</v>
       </c>
-      <c r="N26" s="3">
-        <v>8200</v>
-      </c>
-      <c r="O26" s="3">
-        <v>16000</v>
-      </c>
-      <c r="P26" s="3">
-        <v>9500</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>14600</v>
-      </c>
-      <c r="R26" s="3">
-        <v>13400</v>
-      </c>
-      <c r="S26" s="3">
-        <v>6500</v>
-      </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
-      <c r="U26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="V26" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="W26" s="3">
-        <v>200</v>
-      </c>
-      <c r="X26" s="3">
-        <v>2000</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>3200</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>4300</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>6600</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>4900</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>9800</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>6800</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>5000</v>
-      </c>
-      <c r="AF26" s="3">
-        <v>8400</v>
-      </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="3">
+        <v>7300</v>
+      </c>
+      <c r="L27" s="3">
+        <v>6400</v>
+      </c>
+      <c r="M27" s="3">
+        <v>3500</v>
+      </c>
+      <c r="N27" s="3">
+        <v>8400</v>
+      </c>
+      <c r="O27" s="3">
+        <v>8200</v>
+      </c>
+      <c r="P27" s="3">
+        <v>16000</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>9500</v>
+      </c>
+      <c r="R27" s="3">
+        <v>14600</v>
+      </c>
+      <c r="S27" s="3">
+        <v>13400</v>
+      </c>
+      <c r="T27" s="3">
+        <v>6500</v>
+      </c>
+      <c r="U27" s="3">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="X27" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AA27" s="3">
         <v>4300</v>
       </c>
-      <c r="G27" s="3">
-        <v>6400</v>
-      </c>
-      <c r="H27" s="3">
-        <v>300</v>
-      </c>
-      <c r="I27" s="3">
-        <v>5100</v>
-      </c>
-      <c r="J27" s="3">
-        <v>7300</v>
-      </c>
-      <c r="K27" s="3">
-        <v>6400</v>
-      </c>
-      <c r="L27" s="3">
-        <v>3500</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="AB27" s="3">
+        <v>6600</v>
+      </c>
+      <c r="AC27" s="3">
+        <v>4900</v>
+      </c>
+      <c r="AD27" s="3">
+        <v>9800</v>
+      </c>
+      <c r="AE27" s="3">
+        <v>6800</v>
+      </c>
+      <c r="AF27" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AG27" s="3">
         <v>8400</v>
       </c>
-      <c r="N27" s="3">
-        <v>8200</v>
-      </c>
-      <c r="O27" s="3">
-        <v>16000</v>
-      </c>
-      <c r="P27" s="3">
-        <v>9500</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>14600</v>
-      </c>
-      <c r="R27" s="3">
-        <v>13400</v>
-      </c>
-      <c r="S27" s="3">
-        <v>6500</v>
-      </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
-      <c r="U27" s="3">
-        <v>-200</v>
-      </c>
-      <c r="V27" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="W27" s="3">
-        <v>200</v>
-      </c>
-      <c r="X27" s="3">
-        <v>2000</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>3200</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>4300</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>6600</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>4900</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>9800</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>6800</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>5000</v>
-      </c>
-      <c r="AF27" s="3">
-        <v>8400</v>
-      </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2908,31 +2965,34 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -3018,8 +3078,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3128,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3238,13 +3304,16 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>8</v>
@@ -3252,17 +3321,17 @@
       <c r="F32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -3307,159 +3376,165 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>300</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-200</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
       <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" s="3">
+        <v>7300</v>
+      </c>
+      <c r="L33" s="3">
+        <v>6400</v>
+      </c>
+      <c r="M33" s="3">
+        <v>3500</v>
+      </c>
+      <c r="N33" s="3">
+        <v>8400</v>
+      </c>
+      <c r="O33" s="3">
+        <v>8200</v>
+      </c>
+      <c r="P33" s="3">
+        <v>16000</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>9500</v>
+      </c>
+      <c r="R33" s="3">
+        <v>14600</v>
+      </c>
+      <c r="S33" s="3">
+        <v>13400</v>
+      </c>
+      <c r="T33" s="3">
+        <v>6500</v>
+      </c>
+      <c r="U33" s="3">
+        <v>0</v>
+      </c>
+      <c r="V33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="X33" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y33" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Z33" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AA33" s="3">
         <v>4300</v>
       </c>
-      <c r="G33" s="3">
-        <v>6400</v>
-      </c>
-      <c r="H33" s="3">
-        <v>300</v>
-      </c>
-      <c r="I33" s="3">
-        <v>5100</v>
-      </c>
-      <c r="J33" s="3">
-        <v>7300</v>
-      </c>
-      <c r="K33" s="3">
-        <v>6400</v>
-      </c>
-      <c r="L33" s="3">
-        <v>3500</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="AB33" s="3">
+        <v>6600</v>
+      </c>
+      <c r="AC33" s="3">
+        <v>4900</v>
+      </c>
+      <c r="AD33" s="3">
+        <v>9800</v>
+      </c>
+      <c r="AE33" s="3">
+        <v>6800</v>
+      </c>
+      <c r="AF33" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AG33" s="3">
         <v>8400</v>
       </c>
-      <c r="N33" s="3">
-        <v>8200</v>
-      </c>
-      <c r="O33" s="3">
-        <v>16000</v>
-      </c>
-      <c r="P33" s="3">
-        <v>9500</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>14600</v>
-      </c>
-      <c r="R33" s="3">
-        <v>13400</v>
-      </c>
-      <c r="S33" s="3">
-        <v>6500</v>
-      </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
-      <c r="U33" s="3">
-        <v>-200</v>
-      </c>
-      <c r="V33" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="W33" s="3">
-        <v>200</v>
-      </c>
-      <c r="X33" s="3">
-        <v>2000</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>3200</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>4300</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>6600</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>4900</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>9800</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>6800</v>
-      </c>
-      <c r="AE33" s="3">
-        <v>5000</v>
-      </c>
-      <c r="AF33" s="3">
-        <v>8400</v>
-      </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>3000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3568,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="3">
+        <v>7300</v>
+      </c>
+      <c r="L35" s="3">
+        <v>6400</v>
+      </c>
+      <c r="M35" s="3">
+        <v>3500</v>
+      </c>
+      <c r="N35" s="3">
+        <v>8400</v>
+      </c>
+      <c r="O35" s="3">
+        <v>8200</v>
+      </c>
+      <c r="P35" s="3">
+        <v>16000</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>9500</v>
+      </c>
+      <c r="R35" s="3">
+        <v>14600</v>
+      </c>
+      <c r="S35" s="3">
+        <v>13400</v>
+      </c>
+      <c r="T35" s="3">
+        <v>6500</v>
+      </c>
+      <c r="U35" s="3">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="X35" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y35" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Z35" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AA35" s="3">
         <v>4300</v>
       </c>
-      <c r="G35" s="3">
-        <v>6400</v>
-      </c>
-      <c r="H35" s="3">
-        <v>300</v>
-      </c>
-      <c r="I35" s="3">
-        <v>5100</v>
-      </c>
-      <c r="J35" s="3">
-        <v>7300</v>
-      </c>
-      <c r="K35" s="3">
-        <v>6400</v>
-      </c>
-      <c r="L35" s="3">
-        <v>3500</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="AB35" s="3">
+        <v>6600</v>
+      </c>
+      <c r="AC35" s="3">
+        <v>4900</v>
+      </c>
+      <c r="AD35" s="3">
+        <v>9800</v>
+      </c>
+      <c r="AE35" s="3">
+        <v>6800</v>
+      </c>
+      <c r="AF35" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AG35" s="3">
         <v>8400</v>
       </c>
-      <c r="N35" s="3">
-        <v>8200</v>
-      </c>
-      <c r="O35" s="3">
-        <v>16000</v>
-      </c>
-      <c r="P35" s="3">
-        <v>9500</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>14600</v>
-      </c>
-      <c r="R35" s="3">
-        <v>13400</v>
-      </c>
-      <c r="S35" s="3">
-        <v>6500</v>
-      </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
-      <c r="U35" s="3">
-        <v>-200</v>
-      </c>
-      <c r="V35" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="W35" s="3">
-        <v>200</v>
-      </c>
-      <c r="X35" s="3">
-        <v>2000</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>3200</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>4300</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>6600</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>4900</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>9800</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>6800</v>
-      </c>
-      <c r="AE35" s="3">
-        <v>5000</v>
-      </c>
-      <c r="AF35" s="3">
-        <v>8400</v>
-      </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>3000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E38" s="2">
         <v>45688</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45596</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45504</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45412</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45322</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45230</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45138</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45046</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44957</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44865</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44773</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44681</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44592</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44500</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44408</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44316</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44227</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44135</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44043</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43951</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43861</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43769</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43677</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43585</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43496</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43404</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43312</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43220</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43131</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43039</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42947</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42766</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42674</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3833,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3873,151 +3958,155 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>4900</v>
-      </c>
-      <c r="E41" s="3">
-        <v>2500</v>
-      </c>
-      <c r="F41" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G41" s="3">
-        <v>4400</v>
-      </c>
-      <c r="H41" s="3">
-        <v>3000</v>
-      </c>
-      <c r="I41" s="3">
-        <v>7000</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K41" s="3">
         <v>6200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>12700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7100</v>
-      </c>
-      <c r="S41" s="3">
-        <v>5400</v>
       </c>
       <c r="T41" s="3">
         <v>5400</v>
       </c>
       <c r="U41" s="3">
+        <v>5400</v>
+      </c>
+      <c r="V41" s="3">
         <v>6200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>11300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>7100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>6300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>7200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>8100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>8000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>8400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
-        <v>12200</v>
-      </c>
-      <c r="E42" s="3">
-        <v>16100</v>
-      </c>
-      <c r="F42" s="3">
+      <c r="D42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K42" s="3">
         <v>15900</v>
       </c>
-      <c r="G42" s="3">
-        <v>15400</v>
-      </c>
-      <c r="H42" s="3">
-        <v>14800</v>
-      </c>
-      <c r="I42" s="3">
-        <v>14800</v>
-      </c>
-      <c r="J42" s="3">
-        <v>15900</v>
-      </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>14600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>10600</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>8</v>
       </c>
@@ -4033,8 +4122,8 @@
       <c r="R42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -4093,236 +4182,245 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>61300</v>
-      </c>
-      <c r="E43" s="3">
-        <v>58700</v>
-      </c>
-      <c r="F43" s="3">
-        <v>70200</v>
-      </c>
-      <c r="G43" s="3">
-        <v>70100</v>
-      </c>
-      <c r="H43" s="3">
-        <v>73400</v>
-      </c>
-      <c r="I43" s="3">
-        <v>73600</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K43" s="3">
         <v>68500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>78200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>87000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>87400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>83700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>79500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>83700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>75200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>59900</v>
-      </c>
-      <c r="S43" s="3">
-        <v>45000</v>
       </c>
       <c r="T43" s="3">
         <v>45000</v>
       </c>
       <c r="U43" s="3">
+        <v>45000</v>
+      </c>
+      <c r="V43" s="3">
         <v>48900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>41700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>47300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>54200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>55600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>59400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>67200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>64400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>64700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>76500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>68800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>55500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>54700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>53000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>49500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>43000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>39700</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>39900</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>178800</v>
-      </c>
-      <c r="E44" s="3">
-        <v>174700</v>
-      </c>
-      <c r="F44" s="3">
-        <v>169500</v>
-      </c>
-      <c r="G44" s="3">
-        <v>174900</v>
-      </c>
-      <c r="H44" s="3">
-        <v>181300</v>
-      </c>
-      <c r="I44" s="3">
-        <v>193400</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K44" s="3">
         <v>208000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>208700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>219000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>234700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>244300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>232600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>203000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>149800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>121100</v>
-      </c>
-      <c r="S44" s="3">
-        <v>114900</v>
       </c>
       <c r="T44" s="3">
         <v>114900</v>
       </c>
       <c r="U44" s="3">
+        <v>114900</v>
+      </c>
+      <c r="V44" s="3">
         <v>112500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>135800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>160200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>156300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>168800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>176400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>185800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>197900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>198600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>170900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>153700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>144900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>130700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>124500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>115200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>112600</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>117000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>113400</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>8</v>
@@ -4330,8 +4428,8 @@
       <c r="G45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H45" s="3">
-        <v>0</v>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>8</v>
@@ -4339,202 +4437,208 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L45" s="3">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3">
         <v>15000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>11800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6700</v>
-      </c>
-      <c r="S45" s="3">
-        <v>2400</v>
       </c>
       <c r="T45" s="3">
         <v>2400</v>
       </c>
       <c r="U45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="V45" s="3">
         <v>7400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>11800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>11600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>6700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>5300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>7200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>5700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>5900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>5500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>262300</v>
-      </c>
-      <c r="E46" s="3">
-        <v>261200</v>
-      </c>
-      <c r="F46" s="3">
-        <v>266400</v>
-      </c>
-      <c r="G46" s="3">
-        <v>269600</v>
-      </c>
-      <c r="H46" s="3">
-        <v>277300</v>
-      </c>
-      <c r="I46" s="3">
-        <v>292900</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K46" s="3">
         <v>301100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>309900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>335300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>348800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>352600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>331100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>304000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>240600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>194800</v>
-      </c>
-      <c r="S46" s="3">
-        <v>167700</v>
       </c>
       <c r="T46" s="3">
         <v>167700</v>
       </c>
       <c r="U46" s="3">
+        <v>167700</v>
+      </c>
+      <c r="V46" s="3">
         <v>175100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>187600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>225500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>215800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>242500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>254600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>266400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>270900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>274800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>261700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>232500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>210100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>197600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>190200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>176300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>164800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>166700</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>169300</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4562,8 +4666,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4643,141 +4747,147 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>192000</v>
-      </c>
-      <c r="E48" s="3">
-        <v>191600</v>
-      </c>
-      <c r="F48" s="3">
-        <v>191100</v>
-      </c>
-      <c r="G48" s="3">
-        <v>184000</v>
-      </c>
-      <c r="H48" s="3">
-        <v>182000</v>
-      </c>
-      <c r="I48" s="3">
-        <v>175800</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K48" s="3">
         <v>169100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>160800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>158100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>151000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>145900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>140800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>137800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>137400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>135700</v>
-      </c>
-      <c r="S48" s="3">
-        <v>139000</v>
       </c>
       <c r="T48" s="3">
         <v>139000</v>
       </c>
       <c r="U48" s="3">
+        <v>139000</v>
+      </c>
+      <c r="V48" s="3">
         <v>135400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>134600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>133400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>134700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>122800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>112500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>107900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>104700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>105500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>104200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>102500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>98100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>96100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>97200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>96900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>93700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>93200</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>92600</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>0</v>
-      </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+      <c r="D49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -4863,8 +4973,11 @@
       <c r="AL49" s="3">
         <v>0</v>
       </c>
+      <c r="AM49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4973,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5083,118 +5199,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>15200</v>
-      </c>
-      <c r="E52" s="3">
-        <v>15700</v>
-      </c>
-      <c r="F52" s="3">
-        <v>15600</v>
-      </c>
-      <c r="G52" s="3">
-        <v>16700</v>
-      </c>
-      <c r="H52" s="3">
-        <v>15600</v>
-      </c>
-      <c r="I52" s="3">
-        <v>13500</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K52" s="3">
         <v>13400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9500</v>
-      </c>
-      <c r="P52" s="3">
-        <v>7200</v>
       </c>
       <c r="Q52" s="3">
         <v>7200</v>
       </c>
       <c r="R52" s="3">
+        <v>7200</v>
+      </c>
+      <c r="S52" s="3">
         <v>6200</v>
-      </c>
-      <c r="S52" s="3">
-        <v>6100</v>
       </c>
       <c r="T52" s="3">
         <v>6100</v>
       </c>
       <c r="U52" s="3">
+        <v>6100</v>
+      </c>
+      <c r="V52" s="3">
         <v>6600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4800</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>3900</v>
       </c>
       <c r="Z52" s="3">
         <v>3900</v>
       </c>
       <c r="AA52" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AB52" s="3">
         <v>4500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>4300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>6200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>4600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>4700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5303,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
-        <v>469400</v>
-      </c>
-      <c r="E54" s="3">
-        <v>468500</v>
-      </c>
-      <c r="F54" s="3">
-        <v>473100</v>
-      </c>
-      <c r="G54" s="3">
-        <v>470300</v>
-      </c>
-      <c r="H54" s="3">
-        <v>474800</v>
-      </c>
-      <c r="I54" s="3">
-        <v>482200</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K54" s="3">
         <v>483700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>481700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>503700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>509200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>508100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>481500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>449000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>385200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>336800</v>
-      </c>
-      <c r="S54" s="3">
-        <v>312800</v>
       </c>
       <c r="T54" s="3">
         <v>312800</v>
       </c>
       <c r="U54" s="3">
+        <v>312800</v>
+      </c>
+      <c r="V54" s="3">
         <v>317000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>327700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>363500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>355300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>369200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>371000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>378900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>379900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>384100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>369500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>341200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>313600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>298200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>292200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>275200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>260800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>261400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>263200</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5453,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5493,71 +5622,72 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>31900</v>
-      </c>
-      <c r="E57" s="3">
-        <v>30200</v>
-      </c>
-      <c r="F57" s="3">
-        <v>28100</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K57" s="3">
         <v>33500</v>
       </c>
-      <c r="H57" s="3">
-        <v>26300</v>
-      </c>
-      <c r="I57" s="3">
-        <v>29400</v>
-      </c>
-      <c r="J57" s="3">
-        <v>33500</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>34200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>39000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>39200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>53300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>52800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>38500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>34600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>19000</v>
-      </c>
-      <c r="S57" s="3">
-        <v>16400</v>
       </c>
       <c r="T57" s="3">
         <v>16400</v>
       </c>
       <c r="U57" s="3">
+        <v>16400</v>
+      </c>
+      <c r="V57" s="3">
         <v>8300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>14500</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>8</v>
       </c>
@@ -5570,8 +5700,8 @@
       <c r="AA57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB57" s="3">
-        <v>0</v>
+      <c r="AB57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC57" s="3">
         <v>0</v>
@@ -5603,118 +5733,124 @@
       <c r="AL57" s="3">
         <v>0</v>
       </c>
+      <c r="AM57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>83200</v>
-      </c>
-      <c r="E58" s="3">
-        <v>49400</v>
-      </c>
-      <c r="F58" s="3">
-        <v>54600</v>
-      </c>
-      <c r="G58" s="3">
-        <v>51900</v>
-      </c>
-      <c r="H58" s="3">
-        <v>67100</v>
-      </c>
-      <c r="I58" s="3">
-        <v>68400</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K58" s="3">
         <v>73700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>87100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>106800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>117200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>114800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>113800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>104400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>59000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>32700</v>
-      </c>
-      <c r="S58" s="3">
-        <v>21300</v>
       </c>
       <c r="T58" s="3">
         <v>21300</v>
       </c>
       <c r="U58" s="3">
+        <v>21300</v>
+      </c>
+      <c r="V58" s="3">
         <v>35400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>42000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>74500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>65800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>82500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>88600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>100600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>107100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>111200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>110500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>90700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>77800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>67000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>67900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>56800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>49100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>50200</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>43400</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5742,246 +5878,252 @@
       <c r="K59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M59" s="3">
         <v>34800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>35500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>38100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>35200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>31900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>26900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>23500</v>
-      </c>
-      <c r="S59" s="3">
-        <v>22000</v>
       </c>
       <c r="T59" s="3">
         <v>22000</v>
       </c>
       <c r="U59" s="3">
+        <v>22000</v>
+      </c>
+      <c r="V59" s="3">
         <v>21000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>19500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>40700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>39900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>41800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>46400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>46000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>48100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>52500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>46700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>45300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>36400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>35400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>31400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>29100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>26200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>29200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>144400</v>
-      </c>
-      <c r="E60" s="3">
-        <v>112300</v>
-      </c>
-      <c r="F60" s="3">
-        <v>115800</v>
-      </c>
-      <c r="G60" s="3">
-        <v>118500</v>
-      </c>
-      <c r="H60" s="3">
-        <v>129200</v>
-      </c>
-      <c r="I60" s="3">
-        <v>135500</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K60" s="3">
         <v>142100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>151300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>180600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>192000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>206200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>201800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>174800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>120500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>75200</v>
-      </c>
-      <c r="S60" s="3">
-        <v>59600</v>
       </c>
       <c r="T60" s="3">
         <v>59600</v>
       </c>
       <c r="U60" s="3">
+        <v>59600</v>
+      </c>
+      <c r="V60" s="3">
         <v>64700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>75900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>115200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>105700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>124400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>135000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>146600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>155200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>163600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>157100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>136000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>114200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>102400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>99200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>85900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>75300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>79300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>73500</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D61" s="3">
-        <v>36500</v>
-      </c>
-      <c r="E61" s="3">
-        <v>37200</v>
-      </c>
-      <c r="F61" s="3">
-        <v>37300</v>
-      </c>
-      <c r="G61" s="3">
-        <v>36400</v>
-      </c>
-      <c r="H61" s="3">
-        <v>37700</v>
-      </c>
-      <c r="I61" s="3">
-        <v>39000</v>
-      </c>
-      <c r="J61" s="3">
+      <c r="D61" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K61" s="3">
         <v>39100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>37900</v>
-      </c>
-      <c r="L61" s="3">
-        <v>20500</v>
       </c>
       <c r="M61" s="3">
         <v>20500</v>
       </c>
       <c r="N61" s="3">
+        <v>20500</v>
+      </c>
+      <c r="O61" s="3">
         <v>12600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12800</v>
-      </c>
-      <c r="P61" s="3">
-        <v>12900</v>
       </c>
       <c r="Q61" s="3">
         <v>12900</v>
       </c>
       <c r="R61" s="3">
-        <v>13100</v>
+        <v>12900</v>
       </c>
       <c r="S61" s="3">
         <v>13100</v>
@@ -5990,13 +6132,13 @@
         <v>13100</v>
       </c>
       <c r="U61" s="3">
+        <v>13100</v>
+      </c>
+      <c r="V61" s="3">
         <v>13000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>13100</v>
-      </c>
-      <c r="W61" s="3">
-        <v>12000</v>
       </c>
       <c r="X61" s="3">
         <v>12000</v>
@@ -6005,10 +6147,10 @@
         <v>12000</v>
       </c>
       <c r="Z61" s="3">
+        <v>12000</v>
+      </c>
+      <c r="AA61" s="3">
         <v>12200</v>
-      </c>
-      <c r="AA61" s="3">
-        <v>12000</v>
       </c>
       <c r="AB61" s="3">
         <v>12000</v>
@@ -6043,16 +6185,19 @@
       <c r="AL61" s="3">
         <v>12000</v>
       </c>
+      <c r="AM61" s="3">
+        <v>12000</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E62" s="3">
-        <v>0</v>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>8</v>
@@ -6063,98 +6208,101 @@
       <c r="H62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I62" s="3">
-        <v>0</v>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
         <v>17900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>16000</v>
-      </c>
-      <c r="N62" s="3">
-        <v>17100</v>
       </c>
       <c r="O62" s="3">
         <v>17100</v>
       </c>
       <c r="P62" s="3">
+        <v>17100</v>
+      </c>
+      <c r="Q62" s="3">
         <v>18500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>20600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>23900</v>
-      </c>
-      <c r="S62" s="3">
-        <v>22900</v>
       </c>
       <c r="T62" s="3">
         <v>22900</v>
       </c>
       <c r="U62" s="3">
+        <v>22900</v>
+      </c>
+      <c r="V62" s="3">
         <v>22700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>22200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>19000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>21000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>15100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8700</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>7200</v>
       </c>
       <c r="AB62" s="3">
         <v>7200</v>
       </c>
       <c r="AC62" s="3">
+        <v>7200</v>
+      </c>
+      <c r="AD62" s="3">
         <v>8000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>8800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>7600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>7100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>12300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>12800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>11100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>9100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>8300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6263,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6373,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6483,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>180900</v>
-      </c>
-      <c r="E66" s="3">
-        <v>149500</v>
-      </c>
-      <c r="F66" s="3">
-        <v>154000</v>
-      </c>
-      <c r="G66" s="3">
-        <v>154900</v>
-      </c>
-      <c r="H66" s="3">
-        <v>166800</v>
-      </c>
-      <c r="I66" s="3">
-        <v>174500</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K66" s="3">
         <v>181200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>189200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>219000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>228400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>235900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>231700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>206200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>154100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>112200</v>
-      </c>
-      <c r="S66" s="3">
-        <v>95700</v>
       </c>
       <c r="T66" s="3">
         <v>95700</v>
       </c>
       <c r="U66" s="3">
+        <v>95700</v>
+      </c>
+      <c r="V66" s="3">
         <v>100400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>111200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>146200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>138700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>151500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>155900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>165800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>174400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>183700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>177900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>155600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>133300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>126700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>124000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>109000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>96500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>99700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>102500</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6633,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6743,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6853,31 +7017,34 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D70" s="3">
-        <v>0</v>
-      </c>
-      <c r="E70" s="3">
-        <v>0</v>
-      </c>
-      <c r="F70" s="3">
-        <v>0</v>
-      </c>
-      <c r="G70" s="3">
-        <v>0</v>
-      </c>
-      <c r="H70" s="3">
-        <v>0</v>
-      </c>
-      <c r="I70" s="3">
-        <v>0</v>
-      </c>
-      <c r="J70" s="3">
-        <v>0</v>
+      <c r="D70" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -6963,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7073,71 +7243,74 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>242500</v>
-      </c>
-      <c r="E72" s="3">
-        <v>264400</v>
-      </c>
-      <c r="F72" s="3">
-        <v>264800</v>
-      </c>
-      <c r="G72" s="3">
-        <v>255300</v>
-      </c>
-      <c r="H72" s="3">
-        <v>255300</v>
-      </c>
-      <c r="I72" s="3">
-        <v>255000</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K72" s="3">
         <v>249900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>241600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>235600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>232100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>223800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>201300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>193800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>181000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>171700</v>
-      </c>
-      <c r="S72" s="3">
-        <v>165400</v>
       </c>
       <c r="T72" s="3">
         <v>165400</v>
       </c>
       <c r="U72" s="3">
+        <v>165400</v>
+      </c>
+      <c r="V72" s="3">
         <v>165500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>165600</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>8</v>
       </c>
@@ -7147,21 +7320,21 @@
       <c r="Z72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB72" s="3">
         <v>213100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>205600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>200500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>191500</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>8</v>
       </c>
@@ -7174,8 +7347,8 @@
       <c r="AI72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ72" s="3">
-        <v>0</v>
+      <c r="AJ72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK72" s="3">
         <v>0</v>
@@ -7183,8 +7356,11 @@
       <c r="AL72" s="3">
         <v>0</v>
       </c>
+      <c r="AM72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7293,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7403,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7513,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
-        <v>288600</v>
-      </c>
-      <c r="E76" s="3">
-        <v>319000</v>
-      </c>
-      <c r="F76" s="3">
-        <v>319100</v>
-      </c>
-      <c r="G76" s="3">
-        <v>315400</v>
-      </c>
-      <c r="H76" s="3">
-        <v>308000</v>
-      </c>
-      <c r="I76" s="3">
-        <v>307700</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K76" s="3">
         <v>302500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>292500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>284700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>280700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>272300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>249800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>242800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>231100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>224600</v>
-      </c>
-      <c r="S76" s="3">
-        <v>217100</v>
       </c>
       <c r="T76" s="3">
         <v>217100</v>
       </c>
       <c r="U76" s="3">
+        <v>217100</v>
+      </c>
+      <c r="V76" s="3">
         <v>216600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>216500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>217300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>216600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>217800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>215200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>213100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>205600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>200500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>191500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>185600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>180400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>171500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>168200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>166200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>164400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>161700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>160600</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7733,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E80" s="2">
         <v>45688</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45596</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45504</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45412</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45322</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45230</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45138</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45046</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44957</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44865</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44773</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44681</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44592</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44500</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44408</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44316</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44227</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44135</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44043</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43951</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43861</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43769</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43677</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43585</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43496</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43404</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43312</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43220</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43131</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43039</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42947</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42766</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42674</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" s="3">
+        <v>7300</v>
+      </c>
+      <c r="L81" s="3">
+        <v>6400</v>
+      </c>
+      <c r="M81" s="3">
+        <v>3500</v>
+      </c>
+      <c r="N81" s="3">
+        <v>8400</v>
+      </c>
+      <c r="O81" s="3">
+        <v>8200</v>
+      </c>
+      <c r="P81" s="3">
+        <v>16000</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>9500</v>
+      </c>
+      <c r="R81" s="3">
+        <v>14600</v>
+      </c>
+      <c r="S81" s="3">
+        <v>13400</v>
+      </c>
+      <c r="T81" s="3">
+        <v>6500</v>
+      </c>
+      <c r="U81" s="3">
+        <v>0</v>
+      </c>
+      <c r="V81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="X81" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y81" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Z81" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AA81" s="3">
         <v>4300</v>
       </c>
-      <c r="G81" s="3">
-        <v>6400</v>
-      </c>
-      <c r="H81" s="3">
-        <v>300</v>
-      </c>
-      <c r="I81" s="3">
-        <v>5100</v>
-      </c>
-      <c r="J81" s="3">
-        <v>7300</v>
-      </c>
-      <c r="K81" s="3">
-        <v>6400</v>
-      </c>
-      <c r="L81" s="3">
-        <v>3500</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="AB81" s="3">
+        <v>6600</v>
+      </c>
+      <c r="AC81" s="3">
+        <v>4900</v>
+      </c>
+      <c r="AD81" s="3">
+        <v>9800</v>
+      </c>
+      <c r="AE81" s="3">
+        <v>6800</v>
+      </c>
+      <c r="AF81" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AG81" s="3">
         <v>8400</v>
       </c>
-      <c r="N81" s="3">
-        <v>8200</v>
-      </c>
-      <c r="O81" s="3">
-        <v>16000</v>
-      </c>
-      <c r="P81" s="3">
-        <v>9500</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>14600</v>
-      </c>
-      <c r="R81" s="3">
-        <v>13400</v>
-      </c>
-      <c r="S81" s="3">
-        <v>6500</v>
-      </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
-      <c r="U81" s="3">
-        <v>-200</v>
-      </c>
-      <c r="V81" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="W81" s="3">
-        <v>200</v>
-      </c>
-      <c r="X81" s="3">
-        <v>2000</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>3200</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>4300</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>6600</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>4900</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>9800</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>6800</v>
-      </c>
-      <c r="AE81" s="3">
-        <v>5000</v>
-      </c>
-      <c r="AF81" s="3">
-        <v>8400</v>
-      </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>3000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7998,8 +8195,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8027,44 +8225,44 @@
       <c r="K83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L83" s="3">
-        <v>3300</v>
+      <c r="L83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M83" s="3">
         <v>3300</v>
       </c>
       <c r="N83" s="3">
+        <v>3300</v>
+      </c>
+      <c r="O83" s="3">
         <v>4100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>-10300</v>
-      </c>
-      <c r="R83" s="3">
-        <v>3400</v>
       </c>
       <c r="S83" s="3">
         <v>3400</v>
       </c>
       <c r="T83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="U83" s="3">
         <v>3500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3400</v>
-      </c>
-      <c r="X83" s="3">
-        <v>3500</v>
       </c>
       <c r="Y83" s="3">
         <v>3500</v>
@@ -8073,7 +8271,7 @@
         <v>3500</v>
       </c>
       <c r="AA83" s="3">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="AB83" s="3">
         <v>3400</v>
@@ -8082,22 +8280,22 @@
         <v>3400</v>
       </c>
       <c r="AD83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="AE83" s="3">
         <v>3300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>3100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>3000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>3100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>3000</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>2900</v>
       </c>
       <c r="AJ83" s="3">
         <v>2900</v>
@@ -8106,10 +8304,13 @@
         <v>2900</v>
       </c>
       <c r="AL83" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AM83" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8218,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8328,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8438,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8548,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8658,8 +8871,11 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8687,89 +8903,92 @@
       <c r="K89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M89" s="3">
         <v>6700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-30200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-54700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-6300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>21200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>23600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>5000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>23000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>11100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>22600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>12900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>14800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-9500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-11800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-4300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-2500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-6000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>7800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8808,8 +9027,9 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8837,8 +9057,8 @@
       <c r="K91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -8918,8 +9138,11 @@
       <c r="AL91" s="3">
         <v>0</v>
       </c>
+      <c r="AM91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9028,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9138,8 +9364,11 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9167,8 +9396,8 @@
       <c r="K94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -9191,15 +9420,15 @@
       <c r="S94" s="3">
         <v>0</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U94" s="3">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V94" s="3">
         <v>4100</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>8</v>
       </c>
@@ -9209,8 +9438,8 @@
       <c r="Y94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
+      <c r="Z94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
@@ -9248,8 +9477,11 @@
       <c r="AL94" s="3">
         <v>0</v>
       </c>
+      <c r="AM94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9288,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9317,8 +9550,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9398,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9508,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9618,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9728,8 +9970,11 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9757,8 +10002,8 @@
       <c r="K100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -9838,8 +10083,11 @@
       <c r="AL100" s="3">
         <v>0</v>
       </c>
+      <c r="AM100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9867,8 +10115,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9948,8 +10196,11 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9977,8 +10228,8 @@
       <c r="K102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
+      <c r="L102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M102" s="3">
         <v>0</v>
@@ -10056,6 +10307,9 @@
         <v>0</v>
       </c>
       <c r="AL102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="3">
         <v>0</v>
       </c>
     </row>
